--- a/Result/checksun/貿易百貨.xlsx
+++ b/Result/checksun/貿易百貨.xlsx
@@ -1013,7 +1013,11 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -1301,7 +1305,11 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -1589,7 +1597,11 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -1877,7 +1889,11 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -2165,7 +2181,11 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -2453,7 +2473,11 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -2741,7 +2765,11 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -3029,7 +3057,11 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -3317,7 +3349,11 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -3605,7 +3641,11 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -4185,7 +4225,11 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -4473,7 +4517,11 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -4761,7 +4809,11 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -5049,7 +5101,11 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -5337,7 +5393,11 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -5625,7 +5685,11 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -5913,7 +5977,11 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -6201,7 +6269,11 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -6489,7 +6561,11 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -6777,7 +6853,11 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr"/>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -7357,7 +7437,11 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -7645,7 +7729,11 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -7933,7 +8021,11 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr"/>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -8221,7 +8313,11 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -8509,7 +8605,11 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -8797,7 +8897,11 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr"/>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -9085,7 +9189,11 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr"/>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -9373,7 +9481,11 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr"/>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -9661,7 +9773,11 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -9949,7 +10065,11 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr"/>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -10529,7 +10649,11 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr"/>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -10817,7 +10941,11 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr"/>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -11105,7 +11233,11 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr"/>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -11393,7 +11525,11 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr"/>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -11681,7 +11817,11 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr"/>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -11969,7 +12109,11 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr"/>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -12257,7 +12401,11 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr"/>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -12545,7 +12693,11 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr"/>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -12833,7 +12985,11 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr"/>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -13121,7 +13277,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr"/>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -13701,7 +13861,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr"/>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -13989,7 +14153,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr"/>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -14277,7 +14445,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr"/>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -14565,7 +14737,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr"/>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -14853,7 +15029,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr"/>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -15141,7 +15321,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr"/>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -15429,7 +15613,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr"/>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -15717,7 +15905,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr"/>
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -16005,7 +16197,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr"/>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -16293,7 +16489,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr"/>
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -16873,7 +17073,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr"/>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -17161,7 +17365,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr"/>
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -17449,7 +17657,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr"/>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -17737,7 +17949,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr"/>
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -18025,7 +18241,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr"/>
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -18313,7 +18533,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr"/>
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -18601,7 +18825,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr"/>
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -18889,7 +19117,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr"/>
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -19177,7 +19409,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr"/>
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -19465,7 +19701,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr"/>
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -20045,7 +20285,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr"/>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -20333,7 +20577,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr"/>
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -20621,7 +20869,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr"/>
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -20909,7 +21161,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr"/>
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -21197,7 +21453,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr"/>
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -21485,7 +21745,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr"/>
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -21773,7 +22037,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr"/>
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -22061,7 +22329,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr"/>
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -22349,7 +22621,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr"/>
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -22637,7 +22913,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr"/>
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -23217,7 +23497,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr"/>
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -23505,7 +23789,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr"/>
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -23793,7 +24081,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr"/>
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -24081,7 +24373,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr"/>
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -24369,7 +24665,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr"/>
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -24657,7 +24957,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr"/>
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -24945,7 +25249,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr"/>
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -25233,7 +25541,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr"/>
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -25521,7 +25833,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr"/>
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -25809,7 +26125,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr"/>
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -26389,7 +26709,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr"/>
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -26677,7 +27001,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr"/>
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -26965,7 +27293,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr"/>
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B93" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -27253,7 +27585,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr"/>
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -27541,7 +27877,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr"/>
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B95" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -27829,7 +28169,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr"/>
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -28117,7 +28461,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr"/>
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -28405,7 +28753,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr"/>
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -28693,7 +29045,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr"/>
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B99" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -28981,7 +29337,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr"/>
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B100" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -29561,7 +29921,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr"/>
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B102" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -29849,7 +30213,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr"/>
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B103" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -30137,7 +30505,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr"/>
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B104" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -30425,7 +30797,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr"/>
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B105" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -30713,7 +31089,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr"/>
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B106" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -31001,7 +31381,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr"/>
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B107" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -31289,7 +31673,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr"/>
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B108" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -31577,7 +31965,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr"/>
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B109" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -31865,7 +32257,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr"/>
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B110" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -32153,7 +32549,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr"/>
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B111" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -32733,7 +33133,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr"/>
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B113" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -33021,7 +33425,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr"/>
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B114" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -33309,7 +33717,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr"/>
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B115" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -33597,7 +34009,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr"/>
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B116" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -33885,7 +34301,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr"/>
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B117" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -34173,7 +34593,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr"/>
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B118" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -34461,7 +34885,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr"/>
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B119" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -34749,7 +35177,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr"/>
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B120" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -35037,7 +35469,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr"/>
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B121" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -35325,7 +35761,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr"/>
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B122" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -35905,7 +36345,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr"/>
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B124" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -36193,7 +36637,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr"/>
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B125" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -36481,7 +36929,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr"/>
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B126" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -36769,7 +37221,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr"/>
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B127" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -37057,7 +37513,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr"/>
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B128" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -37345,7 +37805,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr"/>
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B129" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -37633,7 +38097,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr"/>
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B130" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -37921,7 +38389,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="inlineStr"/>
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B131" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -38209,7 +38681,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr"/>
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B132" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -38497,7 +38973,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr"/>
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B133" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -39077,7 +39557,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr"/>
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B135" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -39365,7 +39849,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="inlineStr"/>
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B136" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -39653,7 +40141,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="inlineStr"/>
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B137" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -39941,7 +40433,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="inlineStr"/>
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B138" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -40229,7 +40725,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="inlineStr"/>
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B139" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -40517,7 +41017,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="inlineStr"/>
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B140" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -40805,7 +41309,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr"/>
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B141" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -41093,7 +41601,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr"/>
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B142" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -41381,7 +41893,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" t="inlineStr"/>
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B143" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -41669,7 +42185,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="inlineStr"/>
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B144" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -42249,7 +42769,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="inlineStr"/>
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B146" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -42537,7 +43061,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" t="inlineStr"/>
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B147" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -42825,7 +43353,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="inlineStr"/>
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B148" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -43113,7 +43645,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" t="inlineStr"/>
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B149" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -43401,7 +43937,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" t="inlineStr"/>
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B150" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -43689,7 +44229,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="inlineStr"/>
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B151" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -43977,7 +44521,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="inlineStr"/>
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B152" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -44265,7 +44813,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" t="inlineStr"/>
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B153" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -44553,7 +45105,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" t="inlineStr"/>
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B154" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -44841,7 +45397,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" t="inlineStr"/>
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B155" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -45421,7 +45981,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" t="inlineStr"/>
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B157" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -45709,7 +46273,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" t="inlineStr"/>
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B158" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -45997,7 +46565,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" t="inlineStr"/>
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B159" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -46285,7 +46857,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" t="inlineStr"/>
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B160" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -46573,7 +47149,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" t="inlineStr"/>
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B161" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -46861,7 +47441,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" t="inlineStr"/>
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B162" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -47149,7 +47733,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" t="inlineStr"/>
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B163" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -47437,7 +48025,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" t="inlineStr"/>
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B164" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -47725,7 +48317,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" t="inlineStr"/>
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B165" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -48013,7 +48609,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" t="inlineStr"/>
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B166" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -48301,7 +48901,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" t="inlineStr"/>
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B167" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -48589,7 +49193,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" t="inlineStr"/>
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B168" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -48877,7 +49485,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" t="inlineStr"/>
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B169" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -49165,7 +49777,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" t="inlineStr"/>
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B170" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -49453,7 +50069,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" t="inlineStr"/>
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B171" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -50033,7 +50653,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" t="inlineStr"/>
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B173" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -50321,7 +50945,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" t="inlineStr"/>
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B174" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -50609,7 +51237,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" t="inlineStr"/>
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B175" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -50897,7 +51529,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" t="inlineStr"/>
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B176" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -51185,7 +51821,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" t="inlineStr"/>
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B177" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -51473,7 +52113,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" t="inlineStr"/>
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B178" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -51761,7 +52405,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" t="inlineStr"/>
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B179" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -52049,7 +52697,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" t="inlineStr"/>
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B180" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -52337,7 +52989,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" t="inlineStr"/>
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B181" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -52625,7 +53281,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" t="inlineStr"/>
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B182" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -53205,7 +53865,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" t="inlineStr"/>
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B184" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -53493,7 +54157,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" t="inlineStr"/>
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B185" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -53781,7 +54449,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" t="inlineStr"/>
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B186" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -54069,7 +54741,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" t="inlineStr"/>
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B187" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -54357,7 +55033,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" t="inlineStr"/>
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B188" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -54645,7 +55325,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" t="inlineStr"/>
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B189" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -54933,7 +55617,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" t="inlineStr"/>
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B190" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -55221,7 +55909,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" t="inlineStr"/>
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B191" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -55509,7 +56201,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" t="inlineStr"/>
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B192" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -55797,7 +56493,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" t="inlineStr"/>
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B193" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -56377,7 +57077,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" t="inlineStr"/>
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B195" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -56665,7 +57369,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" t="inlineStr"/>
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B196" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -56953,7 +57661,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" t="inlineStr"/>
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B197" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -57241,7 +57953,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" t="inlineStr"/>
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B198" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -57529,7 +58245,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" t="inlineStr"/>
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B199" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -57817,7 +58537,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" t="inlineStr"/>
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B200" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -58105,7 +58829,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" t="inlineStr"/>
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B201" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -58393,7 +59121,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" t="inlineStr"/>
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B202" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -58681,7 +59413,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" t="inlineStr"/>
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B203" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -58969,7 +59705,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" t="inlineStr"/>
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B204" t="inlineStr">
         <is>
           <t>2025-08-25</t>

--- a/Result/checksun/貿易百貨.xlsx
+++ b/Result/checksun/貿易百貨.xlsx
@@ -66888,7 +66888,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -66908,12 +66908,12 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -66958,7 +66958,7 @@
       </c>
       <c r="U182" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19</t>
         </is>
       </c>
       <c r="V182" t="inlineStr">
@@ -66968,7 +66968,7 @@
       </c>
       <c r="W182" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X182" t="inlineStr">
@@ -67013,12 +67013,12 @@
       </c>
       <c r="AF182" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AG182" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="AH182" t="inlineStr">
@@ -67143,22 +67143,22 @@
       </c>
       <c r="BF182" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10.57121295585749</t>
         </is>
       </c>
       <c r="BG182" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-11.17835437598478</t>
         </is>
       </c>
       <c r="BH182" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-12.89564673076615</t>
         </is>
       </c>
       <c r="BI182" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BJ182" t="inlineStr">
@@ -67168,7 +67168,7 @@
       </c>
       <c r="BK182" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BL182" t="inlineStr">
@@ -67178,27 +67178,27 @@
       </c>
       <c r="BM182" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>60.09%</t>
         </is>
       </c>
       <c r="BN182" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-6.84%</t>
         </is>
       </c>
       <c r="BO182" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>40.77</t>
         </is>
       </c>
       <c r="BP182" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4759</t>
         </is>
       </c>
       <c r="BQ182" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>海運32.66%、租賃21.79%、佣金(百貨-聯營)17.30%、勞務及其他17.21%、百貨-自營10.92%、融資租賃利息收入0.11% (2024年)</t>
         </is>
       </c>
       <c r="BR182" t="inlineStr">
@@ -67213,12 +67213,12 @@
       </c>
       <c r="BT182" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.84</t>
         </is>
       </c>
       <c r="BU182" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 交通運輸及航運 - 散裝航運** 貿易百貨 - 零售通路</t>
         </is>
       </c>
     </row>
@@ -67255,7 +67255,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -67275,184 +67275,184 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
         <is>
+          <t>-0.89</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>-5.12</t>
+        </is>
+      </c>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>-21.69</t>
+        </is>
+      </c>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R183" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="T183" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="V183" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="W183" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="X183" t="inlineStr">
+        <is>
+          <t>2025-03-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Y183" t="inlineStr">
+        <is>
+          <t>2025-02-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="Z183" t="inlineStr">
+        <is>
+          <t>7.79</t>
+        </is>
+      </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
+      <c r="AB183" t="inlineStr">
+        <is>
+          <t>2025-08-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="AC183" t="inlineStr">
+        <is>
+          <t>2025-08-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="AD183" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
+      <c r="AE183" t="inlineStr">
+        <is>
+          <t>6.06</t>
+        </is>
+      </c>
+      <c r="AF183" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AG183" t="inlineStr">
+        <is>
+          <t>1015</t>
+        </is>
+      </c>
+      <c r="AH183" t="inlineStr">
+        <is>
+          <t>-0.69</t>
+        </is>
+      </c>
+      <c r="AI183" t="inlineStr">
+        <is>
+          <t>-0.37</t>
+        </is>
+      </c>
+      <c r="AJ183" t="inlineStr">
+        <is>
+          <t>-1.55</t>
+        </is>
+      </c>
+      <c r="AK183" t="inlineStr">
+        <is>
+          <t>5.79</t>
+        </is>
+      </c>
+      <c r="AL183" t="inlineStr">
+        <is>
+          <t>5.811500000000001</t>
+        </is>
+      </c>
+      <c r="AM183" t="inlineStr">
+        <is>
+          <t>5.903</t>
+        </is>
+      </c>
+      <c r="AN183" t="inlineStr">
+        <is>
+          <t>-29.49</t>
+        </is>
+      </c>
+      <c r="AO183" t="inlineStr">
+        <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AP183" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="AQ183" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="M183" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N183" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O183" t="inlineStr">
-        <is>
-          <t>-5.12</t>
-        </is>
-      </c>
-      <c r="P183" t="inlineStr">
-        <is>
-          <t>-21.69</t>
-        </is>
-      </c>
-      <c r="Q183" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R183" t="inlineStr">
+      <c r="AR183" t="inlineStr">
+        <is>
+          <t>5.555555555555621</t>
+        </is>
+      </c>
+      <c r="AS183" t="inlineStr">
+        <is>
+          <t>-43.47</t>
+        </is>
+      </c>
+      <c r="AT183" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="S183" t="inlineStr">
-        <is>
-          <t>-95.0</t>
-        </is>
-      </c>
-      <c r="T183" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="U183" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V183" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="W183" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="X183" t="inlineStr">
-        <is>
-          <t>2025-03-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="Y183" t="inlineStr">
-        <is>
-          <t>2025-02-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="Z183" t="inlineStr">
-        <is>
-          <t>7.79</t>
-        </is>
-      </c>
-      <c r="AA183" t="inlineStr">
-        <is>
-          <t>7.6</t>
-        </is>
-      </c>
-      <c r="AB183" t="inlineStr">
-        <is>
-          <t>2025-08-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="AC183" t="inlineStr">
-        <is>
-          <t>2025-08-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="AD183" t="inlineStr">
-        <is>
-          <t>6.1</t>
-        </is>
-      </c>
-      <c r="AE183" t="inlineStr">
-        <is>
-          <t>6.06</t>
-        </is>
-      </c>
-      <c r="AF183" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG183" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH183" t="inlineStr">
-        <is>
-          <t>-0.69</t>
-        </is>
-      </c>
-      <c r="AI183" t="inlineStr">
-        <is>
-          <t>-0.37</t>
-        </is>
-      </c>
-      <c r="AJ183" t="inlineStr">
-        <is>
-          <t>-1.55</t>
-        </is>
-      </c>
-      <c r="AK183" t="inlineStr">
-        <is>
-          <t>5.79</t>
-        </is>
-      </c>
-      <c r="AL183" t="inlineStr">
-        <is>
-          <t>5.811500000000001</t>
-        </is>
-      </c>
-      <c r="AM183" t="inlineStr">
-        <is>
-          <t>5.903</t>
-        </is>
-      </c>
-      <c r="AN183" t="inlineStr">
-        <is>
-          <t>-29.49</t>
-        </is>
-      </c>
-      <c r="AO183" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AP183" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
-      <c r="AQ183" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AR183" t="inlineStr">
-        <is>
-          <t>5.555555555555621</t>
-        </is>
-      </c>
-      <c r="AS183" t="inlineStr">
-        <is>
-          <t>-43.47</t>
-        </is>
-      </c>
-      <c r="AT183" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AU183" t="inlineStr">
         <is>
           <t>6057685.2</t>
@@ -67510,22 +67510,22 @@
       </c>
       <c r="BF183" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10.57121295585749</t>
         </is>
       </c>
       <c r="BG183" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-11.17835437598478</t>
         </is>
       </c>
       <c r="BH183" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-12.89564673076615</t>
         </is>
       </c>
       <c r="BI183" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BJ183" t="inlineStr">
@@ -67535,7 +67535,7 @@
       </c>
       <c r="BK183" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BL183" t="inlineStr">
@@ -67545,27 +67545,27 @@
       </c>
       <c r="BM183" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>60.09%</t>
         </is>
       </c>
       <c r="BN183" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-6.84%</t>
         </is>
       </c>
       <c r="BO183" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>40.77</t>
         </is>
       </c>
       <c r="BP183" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4759</t>
         </is>
       </c>
       <c r="BQ183" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>海運32.66%、租賃21.79%、佣金(百貨-聯營)17.30%、勞務及其他17.21%、百貨-自營10.92%、融資租賃利息收入0.11% (2024年)</t>
         </is>
       </c>
       <c r="BR183" t="inlineStr">
@@ -67580,12 +67580,12 @@
       </c>
       <c r="BT183" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.84</t>
         </is>
       </c>
       <c r="BU183" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 交通運輸及航運 - 散裝航運** 貿易百貨 - 零售通路</t>
         </is>
       </c>
     </row>
@@ -67622,7 +67622,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>8.80</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -67642,184 +67642,184 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
         <is>
+          <t>-0.89</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>-4.79</t>
+        </is>
+      </c>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>-21.69</t>
+        </is>
+      </c>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R184" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S184" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="T184" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="V184" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="M184" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N184" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O184" t="inlineStr">
-        <is>
-          <t>-4.79</t>
-        </is>
-      </c>
-      <c r="P184" t="inlineStr">
-        <is>
-          <t>-21.69</t>
-        </is>
-      </c>
-      <c r="Q184" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R184" t="inlineStr">
+      <c r="W184" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="X184" t="inlineStr">
+        <is>
+          <t>2025-03-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Y184" t="inlineStr">
+        <is>
+          <t>2025-02-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="Z184" t="inlineStr">
+        <is>
+          <t>7.79</t>
+        </is>
+      </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
+      <c r="AB184" t="inlineStr">
+        <is>
+          <t>2025-08-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="AC184" t="inlineStr">
+        <is>
+          <t>2025-08-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="AD184" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
+      <c r="AE184" t="inlineStr">
+        <is>
+          <t>6.06</t>
+        </is>
+      </c>
+      <c r="AF184" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AG184" t="inlineStr">
+        <is>
+          <t>1015</t>
+        </is>
+      </c>
+      <c r="AH184" t="inlineStr">
+        <is>
+          <t>-0.69</t>
+        </is>
+      </c>
+      <c r="AI184" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="AJ184" t="inlineStr">
+        <is>
+          <t>-1.72</t>
+        </is>
+      </c>
+      <c r="AK184" t="inlineStr">
+        <is>
+          <t>5.81</t>
+        </is>
+      </c>
+      <c r="AL184" t="inlineStr">
+        <is>
+          <t>5.8085</t>
+        </is>
+      </c>
+      <c r="AM184" t="inlineStr">
+        <is>
+          <t>5.91</t>
+        </is>
+      </c>
+      <c r="AN184" t="inlineStr">
+        <is>
+          <t>9.15</t>
+        </is>
+      </c>
+      <c r="AO184" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="AP184" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="AQ184" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AR184" t="inlineStr">
+        <is>
+          <t>10.00000000000006</t>
+        </is>
+      </c>
+      <c r="AS184" t="inlineStr">
+        <is>
+          <t>-40.87</t>
+        </is>
+      </c>
+      <c r="AT184" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="S184" t="inlineStr">
-        <is>
-          <t>-95.0</t>
-        </is>
-      </c>
-      <c r="T184" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U184" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V184" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="W184" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="X184" t="inlineStr">
-        <is>
-          <t>2025-03-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="Y184" t="inlineStr">
-        <is>
-          <t>2025-02-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="Z184" t="inlineStr">
-        <is>
-          <t>7.79</t>
-        </is>
-      </c>
-      <c r="AA184" t="inlineStr">
-        <is>
-          <t>7.6</t>
-        </is>
-      </c>
-      <c r="AB184" t="inlineStr">
-        <is>
-          <t>2025-08-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="AC184" t="inlineStr">
-        <is>
-          <t>2025-08-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="AD184" t="inlineStr">
-        <is>
-          <t>6.1</t>
-        </is>
-      </c>
-      <c r="AE184" t="inlineStr">
-        <is>
-          <t>6.06</t>
-        </is>
-      </c>
-      <c r="AF184" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG184" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH184" t="inlineStr">
-        <is>
-          <t>-0.69</t>
-        </is>
-      </c>
-      <c r="AI184" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
-      <c r="AJ184" t="inlineStr">
-        <is>
-          <t>-1.72</t>
-        </is>
-      </c>
-      <c r="AK184" t="inlineStr">
-        <is>
-          <t>5.81</t>
-        </is>
-      </c>
-      <c r="AL184" t="inlineStr">
-        <is>
-          <t>5.8085</t>
-        </is>
-      </c>
-      <c r="AM184" t="inlineStr">
-        <is>
-          <t>5.91</t>
-        </is>
-      </c>
-      <c r="AN184" t="inlineStr">
-        <is>
-          <t>9.15</t>
-        </is>
-      </c>
-      <c r="AO184" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
-      <c r="AP184" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
-      <c r="AQ184" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AR184" t="inlineStr">
-        <is>
-          <t>10.00000000000006</t>
-        </is>
-      </c>
-      <c r="AS184" t="inlineStr">
-        <is>
-          <t>-40.87</t>
-        </is>
-      </c>
-      <c r="AT184" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AU184" t="inlineStr">
         <is>
           <t>6355087.2</t>
@@ -67872,27 +67872,27 @@
       </c>
       <c r="BE184" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BF184" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10.57121295585749</t>
         </is>
       </c>
       <c r="BG184" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-11.17835437598478</t>
         </is>
       </c>
       <c r="BH184" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-12.89564673076615</t>
         </is>
       </c>
       <c r="BI184" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BJ184" t="inlineStr">
@@ -67902,7 +67902,7 @@
       </c>
       <c r="BK184" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BL184" t="inlineStr">
@@ -67912,27 +67912,27 @@
       </c>
       <c r="BM184" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>60.09%</t>
         </is>
       </c>
       <c r="BN184" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-6.84%</t>
         </is>
       </c>
       <c r="BO184" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>40.77</t>
         </is>
       </c>
       <c r="BP184" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4759</t>
         </is>
       </c>
       <c r="BQ184" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>海運32.66%、租賃21.79%、佣金(百貨-聯營)17.30%、勞務及其他17.21%、百貨-自營10.92%、融資租賃利息收入0.11% (2024年)</t>
         </is>
       </c>
       <c r="BR184" t="inlineStr">
@@ -67947,12 +67947,12 @@
       </c>
       <c r="BT184" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.84</t>
         </is>
       </c>
       <c r="BU184" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 交通運輸及航運 - 散裝航運** 貿易百貨 - 零售通路</t>
         </is>
       </c>
     </row>
@@ -67989,7 +67989,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -68009,12 +68009,12 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -68059,7 +68059,7 @@
       </c>
       <c r="U185" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15</t>
         </is>
       </c>
       <c r="V185" t="inlineStr">
@@ -68069,7 +68069,7 @@
       </c>
       <c r="W185" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="X185" t="inlineStr">
@@ -68114,12 +68114,12 @@
       </c>
       <c r="AF185" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AG185" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="AH185" t="inlineStr">
@@ -68244,22 +68244,22 @@
       </c>
       <c r="BF185" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10.57121295585749</t>
         </is>
       </c>
       <c r="BG185" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-11.17835437598478</t>
         </is>
       </c>
       <c r="BH185" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-12.89564673076615</t>
         </is>
       </c>
       <c r="BI185" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BJ185" t="inlineStr">
@@ -68269,7 +68269,7 @@
       </c>
       <c r="BK185" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BL185" t="inlineStr">
@@ -68279,27 +68279,27 @@
       </c>
       <c r="BM185" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>60.09%</t>
         </is>
       </c>
       <c r="BN185" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-6.84%</t>
         </is>
       </c>
       <c r="BO185" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>40.77</t>
         </is>
       </c>
       <c r="BP185" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4759</t>
         </is>
       </c>
       <c r="BQ185" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>海運32.66%、租賃21.79%、佣金(百貨-聯營)17.30%、勞務及其他17.21%、百貨-自營10.92%、融資租賃利息收入0.11% (2024年)</t>
         </is>
       </c>
       <c r="BR185" t="inlineStr">
@@ -68314,12 +68314,12 @@
       </c>
       <c r="BT185" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.84</t>
         </is>
       </c>
       <c r="BU185" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 交通運輸及航運 - 散裝航運** 貿易百貨 - 零售通路</t>
         </is>
       </c>
     </row>
@@ -68356,7 +68356,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -68376,184 +68376,184 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
         <is>
+          <t>-0.89</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>-4.13</t>
+        </is>
+      </c>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>-21.69</t>
+        </is>
+      </c>
+      <c r="Q186" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R186" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="V186" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="M186" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N186" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O186" t="inlineStr">
-        <is>
-          <t>-4.13</t>
-        </is>
-      </c>
-      <c r="P186" t="inlineStr">
-        <is>
-          <t>-21.69</t>
-        </is>
-      </c>
-      <c r="Q186" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R186" t="inlineStr">
+      <c r="W186" t="inlineStr">
+        <is>
+          <t>-3.0</t>
+        </is>
+      </c>
+      <c r="X186" t="inlineStr">
+        <is>
+          <t>2025-03-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Y186" t="inlineStr">
+        <is>
+          <t>2025-02-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="Z186" t="inlineStr">
+        <is>
+          <t>7.79</t>
+        </is>
+      </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
+      <c r="AB186" t="inlineStr">
+        <is>
+          <t>2025-08-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="AC186" t="inlineStr">
+        <is>
+          <t>2025-08-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="AD186" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
+      <c r="AE186" t="inlineStr">
+        <is>
+          <t>6.06</t>
+        </is>
+      </c>
+      <c r="AF186" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AG186" t="inlineStr">
+        <is>
+          <t>1015</t>
+        </is>
+      </c>
+      <c r="AH186" t="inlineStr">
+        <is>
+          <t>-1.09</t>
+        </is>
+      </c>
+      <c r="AI186" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="AJ186" t="inlineStr">
+        <is>
+          <t>-2.03</t>
+        </is>
+      </c>
+      <c r="AK186" t="inlineStr">
+        <is>
+          <t>5.874000000000001</t>
+        </is>
+      </c>
+      <c r="AL186" t="inlineStr">
+        <is>
+          <t>5.804</t>
+        </is>
+      </c>
+      <c r="AM186" t="inlineStr">
+        <is>
+          <t>5.923999999999999</t>
+        </is>
+      </c>
+      <c r="AN186" t="inlineStr">
+        <is>
+          <t>74.39</t>
+        </is>
+      </c>
+      <c r="AO186" t="inlineStr">
+        <is>
+          <t>-0.00</t>
+        </is>
+      </c>
+      <c r="AP186" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="AQ186" t="inlineStr">
+        <is>
+          <t>13.33333333333331</t>
+        </is>
+      </c>
+      <c r="AR186" t="inlineStr">
+        <is>
+          <t>25.02645502645497</t>
+        </is>
+      </c>
+      <c r="AS186" t="inlineStr">
+        <is>
+          <t>-36.07</t>
+        </is>
+      </c>
+      <c r="AT186" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="S186" t="inlineStr">
-        <is>
-          <t>-95.0</t>
-        </is>
-      </c>
-      <c r="T186" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
-      </c>
-      <c r="U186" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V186" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="W186" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="X186" t="inlineStr">
-        <is>
-          <t>2025-03-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="Y186" t="inlineStr">
-        <is>
-          <t>2025-02-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="Z186" t="inlineStr">
-        <is>
-          <t>7.79</t>
-        </is>
-      </c>
-      <c r="AA186" t="inlineStr">
-        <is>
-          <t>7.6</t>
-        </is>
-      </c>
-      <c r="AB186" t="inlineStr">
-        <is>
-          <t>2025-08-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="AC186" t="inlineStr">
-        <is>
-          <t>2025-08-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="AD186" t="inlineStr">
-        <is>
-          <t>6.1</t>
-        </is>
-      </c>
-      <c r="AE186" t="inlineStr">
-        <is>
-          <t>6.06</t>
-        </is>
-      </c>
-      <c r="AF186" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG186" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH186" t="inlineStr">
-        <is>
-          <t>-1.09</t>
-        </is>
-      </c>
-      <c r="AI186" t="inlineStr">
-        <is>
-          <t>1.21</t>
-        </is>
-      </c>
-      <c r="AJ186" t="inlineStr">
-        <is>
-          <t>-2.03</t>
-        </is>
-      </c>
-      <c r="AK186" t="inlineStr">
-        <is>
-          <t>5.874000000000001</t>
-        </is>
-      </c>
-      <c r="AL186" t="inlineStr">
-        <is>
-          <t>5.804</t>
-        </is>
-      </c>
-      <c r="AM186" t="inlineStr">
-        <is>
-          <t>5.923999999999999</t>
-        </is>
-      </c>
-      <c r="AN186" t="inlineStr">
-        <is>
-          <t>74.39</t>
-        </is>
-      </c>
-      <c r="AO186" t="inlineStr">
-        <is>
-          <t>-0.00</t>
-        </is>
-      </c>
-      <c r="AP186" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
-      <c r="AQ186" t="inlineStr">
-        <is>
-          <t>13.33333333333331</t>
-        </is>
-      </c>
-      <c r="AR186" t="inlineStr">
-        <is>
-          <t>25.02645502645497</t>
-        </is>
-      </c>
-      <c r="AS186" t="inlineStr">
-        <is>
-          <t>-36.07</t>
-        </is>
-      </c>
-      <c r="AT186" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AU186" t="inlineStr">
         <is>
           <t>6984305.6</t>
@@ -68611,22 +68611,22 @@
       </c>
       <c r="BF186" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10.57121295585749</t>
         </is>
       </c>
       <c r="BG186" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-11.17835437598478</t>
         </is>
       </c>
       <c r="BH186" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-12.89564673076615</t>
         </is>
       </c>
       <c r="BI186" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BJ186" t="inlineStr">
@@ -68636,7 +68636,7 @@
       </c>
       <c r="BK186" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BL186" t="inlineStr">
@@ -68646,27 +68646,27 @@
       </c>
       <c r="BM186" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>60.09%</t>
         </is>
       </c>
       <c r="BN186" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-6.84%</t>
         </is>
       </c>
       <c r="BO186" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>40.77</t>
         </is>
       </c>
       <c r="BP186" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4759</t>
         </is>
       </c>
       <c r="BQ186" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>海運32.66%、租賃21.79%、佣金(百貨-聯營)17.30%、勞務及其他17.21%、百貨-自營10.92%、融資租賃利息收入0.11% (2024年)</t>
         </is>
       </c>
       <c r="BR186" t="inlineStr">
@@ -68681,12 +68681,12 @@
       </c>
       <c r="BT186" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.84</t>
         </is>
       </c>
       <c r="BU186" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 交通運輸及航運 - 散裝航運** 貿易百貨 - 零售通路</t>
         </is>
       </c>
     </row>
@@ -68723,7 +68723,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -68743,12 +68743,12 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -68793,7 +68793,7 @@
       </c>
       <c r="U187" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20</t>
         </is>
       </c>
       <c r="V187" t="inlineStr">
@@ -68803,7 +68803,7 @@
       </c>
       <c r="W187" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="X187" t="inlineStr">
@@ -68848,12 +68848,12 @@
       </c>
       <c r="AF187" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AG187" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="AH187" t="inlineStr">
@@ -68978,22 +68978,22 @@
       </c>
       <c r="BF187" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10.57121295585749</t>
         </is>
       </c>
       <c r="BG187" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-11.17835437598478</t>
         </is>
       </c>
       <c r="BH187" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-12.89564673076615</t>
         </is>
       </c>
       <c r="BI187" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BJ187" t="inlineStr">
@@ -69003,7 +69003,7 @@
       </c>
       <c r="BK187" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BL187" t="inlineStr">
@@ -69013,27 +69013,27 @@
       </c>
       <c r="BM187" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>60.09%</t>
         </is>
       </c>
       <c r="BN187" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-6.84%</t>
         </is>
       </c>
       <c r="BO187" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>40.77</t>
         </is>
       </c>
       <c r="BP187" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4759</t>
         </is>
       </c>
       <c r="BQ187" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>海運32.66%、租賃21.79%、佣金(百貨-聯營)17.30%、勞務及其他17.21%、百貨-自營10.92%、融資租賃利息收入0.11% (2024年)</t>
         </is>
       </c>
       <c r="BR187" t="inlineStr">
@@ -69048,12 +69048,12 @@
       </c>
       <c r="BT187" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.84</t>
         </is>
       </c>
       <c r="BU187" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 交通運輸及航運 - 散裝航運** 貿易百貨 - 零售通路</t>
         </is>
       </c>
     </row>
@@ -69090,7 +69090,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>6.20</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -69110,12 +69110,12 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
@@ -69160,7 +69160,7 @@
       </c>
       <c r="U188" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21</t>
         </is>
       </c>
       <c r="V188" t="inlineStr">
@@ -69170,7 +69170,7 @@
       </c>
       <c r="W188" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-10.0</t>
         </is>
       </c>
       <c r="X188" t="inlineStr">
@@ -69215,12 +69215,12 @@
       </c>
       <c r="AF188" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AG188" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="AH188" t="inlineStr">
@@ -69345,22 +69345,22 @@
       </c>
       <c r="BF188" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10.57121295585749</t>
         </is>
       </c>
       <c r="BG188" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-11.17835437598478</t>
         </is>
       </c>
       <c r="BH188" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-12.89564673076615</t>
         </is>
       </c>
       <c r="BI188" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BJ188" t="inlineStr">
@@ -69370,7 +69370,7 @@
       </c>
       <c r="BK188" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BL188" t="inlineStr">
@@ -69380,27 +69380,27 @@
       </c>
       <c r="BM188" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>60.09%</t>
         </is>
       </c>
       <c r="BN188" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-6.84%</t>
         </is>
       </c>
       <c r="BO188" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>40.77</t>
         </is>
       </c>
       <c r="BP188" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4759</t>
         </is>
       </c>
       <c r="BQ188" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>海運32.66%、租賃21.79%、佣金(百貨-聯營)17.30%、勞務及其他17.21%、百貨-自營10.92%、融資租賃利息收入0.11% (2024年)</t>
         </is>
       </c>
       <c r="BR188" t="inlineStr">
@@ -69415,12 +69415,12 @@
       </c>
       <c r="BT188" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.84</t>
         </is>
       </c>
       <c r="BU188" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 交通運輸及航運 - 散裝航運** 貿易百貨 - 零售通路</t>
         </is>
       </c>
     </row>
@@ -69457,7 +69457,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>8.77</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -69477,12 +69477,12 @@
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
@@ -69527,7 +69527,7 @@
       </c>
       <c r="U189" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31</t>
         </is>
       </c>
       <c r="V189" t="inlineStr">
@@ -69537,7 +69537,7 @@
       </c>
       <c r="W189" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="X189" t="inlineStr">
@@ -69582,12 +69582,12 @@
       </c>
       <c r="AF189" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AG189" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="AH189" t="inlineStr">
@@ -69707,27 +69707,27 @@
       </c>
       <c r="BE189" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BF189" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10.57121295585749</t>
         </is>
       </c>
       <c r="BG189" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-11.17835437598478</t>
         </is>
       </c>
       <c r="BH189" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-12.89564673076615</t>
         </is>
       </c>
       <c r="BI189" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="BJ189" t="inlineStr">
@@ -69737,7 +69737,7 @@
       </c>
       <c r="BK189" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BL189" t="inlineStr">
@@ -69747,27 +69747,27 @@
       </c>
       <c r="BM189" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>60.09%</t>
         </is>
       </c>
       <c r="BN189" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-6.84%</t>
         </is>
       </c>
       <c r="BO189" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>40.77</t>
         </is>
       </c>
       <c r="BP189" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4759</t>
         </is>
       </c>
       <c r="BQ189" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>海運32.66%、租賃21.79%、佣金(百貨-聯營)17.30%、勞務及其他17.21%、百貨-自營10.92%、融資租賃利息收入0.11% (2024年)</t>
         </is>
       </c>
       <c r="BR189" t="inlineStr">
@@ -69782,12 +69782,12 @@
       </c>
       <c r="BT189" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.84</t>
         </is>
       </c>
       <c r="BU189" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 交通運輸及航運 - 散裝航運** 貿易百貨 - 零售通路</t>
         </is>
       </c>
     </row>
@@ -69824,7 +69824,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>6.84</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -69844,184 +69844,184 @@
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-3.12</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
         <is>
+          <t>-0.89</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>-1.82</t>
+        </is>
+      </c>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>-21.69</t>
+        </is>
+      </c>
+      <c r="Q190" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R190" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="T190" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V190" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="M190" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N190" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O190" t="inlineStr">
-        <is>
-          <t>-1.82</t>
-        </is>
-      </c>
-      <c r="P190" t="inlineStr">
-        <is>
-          <t>-21.69</t>
-        </is>
-      </c>
-      <c r="Q190" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R190" t="inlineStr">
+      <c r="W190" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="X190" t="inlineStr">
+        <is>
+          <t>2025-03-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Y190" t="inlineStr">
+        <is>
+          <t>2025-02-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="Z190" t="inlineStr">
+        <is>
+          <t>7.79</t>
+        </is>
+      </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
+      <c r="AB190" t="inlineStr">
+        <is>
+          <t>2025-08-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="AC190" t="inlineStr">
+        <is>
+          <t>2025-08-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="AD190" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
+      <c r="AE190" t="inlineStr">
+        <is>
+          <t>6.06</t>
+        </is>
+      </c>
+      <c r="AF190" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AG190" t="inlineStr">
+        <is>
+          <t>1015</t>
+        </is>
+      </c>
+      <c r="AH190" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="AI190" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="AJ190" t="inlineStr">
+        <is>
+          <t>-2.14</t>
+        </is>
+      </c>
+      <c r="AK190" t="inlineStr">
+        <is>
+          <t>5.895999999999999</t>
+        </is>
+      </c>
+      <c r="AL190" t="inlineStr">
+        <is>
+          <t>5.808</t>
+        </is>
+      </c>
+      <c r="AM190" t="inlineStr">
+        <is>
+          <t>5.9352</t>
+        </is>
+      </c>
+      <c r="AN190" t="inlineStr">
+        <is>
+          <t>91.21</t>
+        </is>
+      </c>
+      <c r="AO190" t="inlineStr">
+        <is>
+          <t>-0.00</t>
+        </is>
+      </c>
+      <c r="AP190" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AQ190" t="inlineStr">
+        <is>
+          <t>66.66666666666666</t>
+        </is>
+      </c>
+      <c r="AR190" t="inlineStr">
+        <is>
+          <t>71.29629629629626</t>
+        </is>
+      </c>
+      <c r="AS190" t="inlineStr">
+        <is>
+          <t>52.91</t>
+        </is>
+      </c>
+      <c r="AT190" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="S190" t="inlineStr">
-        <is>
-          <t>-95.0</t>
-        </is>
-      </c>
-      <c r="T190" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U190" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V190" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="W190" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="X190" t="inlineStr">
-        <is>
-          <t>2025-03-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="Y190" t="inlineStr">
-        <is>
-          <t>2025-02-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="Z190" t="inlineStr">
-        <is>
-          <t>7.79</t>
-        </is>
-      </c>
-      <c r="AA190" t="inlineStr">
-        <is>
-          <t>7.6</t>
-        </is>
-      </c>
-      <c r="AB190" t="inlineStr">
-        <is>
-          <t>2025-08-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="AC190" t="inlineStr">
-        <is>
-          <t>2025-08-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="AD190" t="inlineStr">
-        <is>
-          <t>6.1</t>
-        </is>
-      </c>
-      <c r="AE190" t="inlineStr">
-        <is>
-          <t>6.06</t>
-        </is>
-      </c>
-      <c r="AF190" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG190" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH190" t="inlineStr">
-        <is>
-          <t>0.92</t>
-        </is>
-      </c>
-      <c r="AI190" t="inlineStr">
-        <is>
-          <t>1.52</t>
-        </is>
-      </c>
-      <c r="AJ190" t="inlineStr">
-        <is>
-          <t>-2.14</t>
-        </is>
-      </c>
-      <c r="AK190" t="inlineStr">
-        <is>
-          <t>5.895999999999999</t>
-        </is>
-      </c>
-      <c r="AL190" t="inlineStr">
-        <is>
-          <t>5.808</t>
-        </is>
-      </c>
-      <c r="AM190" t="inlineStr">
-        <is>
-          <t>5.9352</t>
-        </is>
-      </c>
-      <c r="AN190" t="inlineStr">
-        <is>
-          <t>91.21</t>
-        </is>
-      </c>
-      <c r="AO190" t="inlineStr">
-        <is>
-          <t>-0.00</t>
-        </is>
-      </c>
-      <c r="AP190" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
-      <c r="AQ190" t="inlineStr">
-        <is>
-          <t>66.66666666666666</t>
-        </is>
-      </c>
-      <c r="AR190" t="inlineStr">
-        <is>
-          <t>71.29629629629626</t>
-        </is>
-      </c>
-      <c r="AS190" t="inlineStr">
-        <is>
-          <t>52.91</t>
-        </is>
-      </c>
-      <c r="AT190" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AU190" t="inlineStr">
         <is>
           <t>15664716.4</t>
@@ -70079,22 +70079,22 @@
       </c>
       <c r="BF190" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10.57121295585749</t>
         </is>
       </c>
       <c r="BG190" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-11.17835437598478</t>
         </is>
       </c>
       <c r="BH190" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-12.89564673076615</t>
         </is>
       </c>
       <c r="BI190" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="BJ190" t="inlineStr">
@@ -70104,7 +70104,7 @@
       </c>
       <c r="BK190" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BL190" t="inlineStr">
@@ -70114,27 +70114,27 @@
       </c>
       <c r="BM190" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>60.09%</t>
         </is>
       </c>
       <c r="BN190" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-6.84%</t>
         </is>
       </c>
       <c r="BO190" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>40.77</t>
         </is>
       </c>
       <c r="BP190" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4759</t>
         </is>
       </c>
       <c r="BQ190" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>海運32.66%、租賃21.79%、佣金(百貨-聯營)17.30%、勞務及其他17.21%、百貨-自營10.92%、融資租賃利息收入0.11% (2024年)</t>
         </is>
       </c>
       <c r="BR190" t="inlineStr">
@@ -70149,12 +70149,12 @@
       </c>
       <c r="BT190" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.84</t>
         </is>
       </c>
       <c r="BU190" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 交通運輸及航運 - 散裝航運** 貿易百貨 - 零售通路</t>
         </is>
       </c>
     </row>
@@ -70191,7 +70191,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>15.51</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -70211,12 +70211,12 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -70316,12 +70316,12 @@
       </c>
       <c r="AF191" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AG191" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="AH191" t="inlineStr">
@@ -70446,22 +70446,22 @@
       </c>
       <c r="BF191" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10.57121295585749</t>
         </is>
       </c>
       <c r="BG191" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-11.17835437598478</t>
         </is>
       </c>
       <c r="BH191" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-12.89564673076615</t>
         </is>
       </c>
       <c r="BI191" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="BJ191" t="inlineStr">
@@ -70471,7 +70471,7 @@
       </c>
       <c r="BK191" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BL191" t="inlineStr">
@@ -70481,27 +70481,27 @@
       </c>
       <c r="BM191" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>60.09%</t>
         </is>
       </c>
       <c r="BN191" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-6.84%</t>
         </is>
       </c>
       <c r="BO191" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>40.77</t>
         </is>
       </c>
       <c r="BP191" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4759</t>
         </is>
       </c>
       <c r="BQ191" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>海運32.66%、租賃21.79%、佣金(百貨-聯營)17.30%、勞務及其他17.21%、百貨-自營10.92%、融資租賃利息收入0.11% (2024年)</t>
         </is>
       </c>
       <c r="BR191" t="inlineStr">
@@ -70516,12 +70516,12 @@
       </c>
       <c r="BT191" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.84</t>
         </is>
       </c>
       <c r="BU191" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 交通運輸及航運 - 散裝航運** 貿易百貨 - 零售通路</t>
         </is>
       </c>
     </row>

--- a/Result/checksun/貿易百貨.xlsx
+++ b/Result/checksun/貿易百貨.xlsx
@@ -1011,15 +1011,11 @@
           <t>11.8575</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>11.974</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>11.950625</t>
-        </is>
+      <c r="AN2" t="n">
+        <v>11.974</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>11.950625</v>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
@@ -1398,15 +1394,11 @@
           <t>11.88</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>11.979</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>11.955</t>
-        </is>
+      <c r="AN3" t="n">
+        <v>11.979</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>11.955</v>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
@@ -1785,15 +1777,11 @@
           <t>11.9</t>
         </is>
       </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>11.983</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>11.95875</t>
-        </is>
+      <c r="AN4" t="n">
+        <v>11.983</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>11.95875</v>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
@@ -2172,15 +2160,11 @@
           <t>11.9175</t>
         </is>
       </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>11.984</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>11.96375</t>
-        </is>
+      <c r="AN5" t="n">
+        <v>11.984</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>11.96375</v>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
@@ -2559,15 +2543,11 @@
           <t>11.935</t>
         </is>
       </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>11.987</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>11.969375</t>
-        </is>
+      <c r="AN6" t="n">
+        <v>11.987</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>11.969375</v>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
@@ -2946,15 +2926,11 @@
           <t>11.9525</t>
         </is>
       </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>11.987</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>11.975</t>
-        </is>
+      <c r="AN7" t="n">
+        <v>11.987</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>11.975</v>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
@@ -3333,15 +3309,11 @@
           <t>11.9725</t>
         </is>
       </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>11.989</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>11.980625</t>
-        </is>
+      <c r="AN8" t="n">
+        <v>11.989</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>11.980625</v>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
@@ -3720,15 +3692,11 @@
           <t>11.995</t>
         </is>
       </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>11.989</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>11.98625</t>
-        </is>
+      <c r="AN9" t="n">
+        <v>11.989</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>11.98625</v>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
@@ -4107,15 +4075,11 @@
           <t>12.0125</t>
         </is>
       </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>11.99</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>11.9925</t>
-        </is>
+      <c r="AN10" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>11.9925</v>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
@@ -4494,15 +4458,11 @@
           <t>12.03</t>
         </is>
       </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>11.989</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>11.99875</t>
-        </is>
+      <c r="AN11" t="n">
+        <v>11.989</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>11.99875</v>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
@@ -4881,15 +4841,11 @@
           <t>7.987</t>
         </is>
       </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>7.925</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>7.90625</t>
-        </is>
+      <c r="AN12" t="n">
+        <v>7.925</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>7.90625</v>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
@@ -5268,15 +5224,11 @@
           <t>8.001000000000001</t>
         </is>
       </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>7.931799999999999</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>7.911375</t>
-        </is>
+      <c r="AN13" t="n">
+        <v>7.931799999999999</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>7.911375</v>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
@@ -5655,15 +5607,11 @@
           <t>8.004999999999999</t>
         </is>
       </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>7.9348</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>7.91525</t>
-        </is>
+      <c r="AN14" t="n">
+        <v>7.9348</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>7.91525</v>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
@@ -6042,15 +5990,11 @@
           <t>8.013000000000002</t>
         </is>
       </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>7.938</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>7.919875</t>
-        </is>
+      <c r="AN15" t="n">
+        <v>7.938</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>7.919875</v>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
@@ -6429,15 +6373,11 @@
           <t>8.014</t>
         </is>
       </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>7.937799999999999</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>7.922874999999999</t>
-        </is>
+      <c r="AN16" t="n">
+        <v>7.937799999999999</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>7.922874999999999</v>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
@@ -6816,15 +6756,11 @@
           <t>8.013</t>
         </is>
       </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>7.936599999999999</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>7.925749999999999</t>
-        </is>
+      <c r="AN17" t="n">
+        <v>7.936599999999999</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>7.925749999999999</v>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
@@ -7203,15 +7139,11 @@
           <t>8.0115</t>
         </is>
       </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>7.934200000000001</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>7.927249999999999</t>
-        </is>
+      <c r="AN18" t="n">
+        <v>7.934200000000001</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>7.927249999999999</v>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
@@ -7590,15 +7522,11 @@
           <t>8.006499999999999</t>
         </is>
       </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>7.931199999999999</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>7.928750000000001</t>
-        </is>
+      <c r="AN19" t="n">
+        <v>7.931199999999999</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>7.928750000000001</v>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
@@ -7977,15 +7905,11 @@
           <t>8.000499999999999</t>
         </is>
       </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>7.9278</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>7.930124999999999</t>
-        </is>
+      <c r="AN20" t="n">
+        <v>7.9278</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>7.930124999999999</v>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
@@ -8364,15 +8288,11 @@
           <t>7.991999999999999</t>
         </is>
       </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>7.927</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>7.931125</t>
-        </is>
+      <c r="AN21" t="n">
+        <v>7.927</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>7.931125</v>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
@@ -8751,15 +8671,11 @@
           <t>5.886</t>
         </is>
       </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>5.9774</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>6.109875000000001</t>
-        </is>
+      <c r="AN22" t="n">
+        <v>5.9774</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>6.109875000000001</v>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
@@ -9138,15 +9054,11 @@
           <t>5.891</t>
         </is>
       </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>5.9864</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>6.116375</t>
-        </is>
+      <c r="AN23" t="n">
+        <v>5.9864</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>6.116375</v>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
@@ -9525,15 +9437,11 @@
           <t>5.897</t>
         </is>
       </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>5.9922</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>6.123375</t>
-        </is>
+      <c r="AN24" t="n">
+        <v>5.9922</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>6.123375</v>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
@@ -9912,15 +9820,11 @@
           <t>5.904500000000001</t>
         </is>
       </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>5.999</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>6.132624999999999</t>
-        </is>
+      <c r="AN25" t="n">
+        <v>5.999</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>6.132624999999999</v>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
@@ -10299,15 +10203,11 @@
           <t>5.9105</t>
         </is>
       </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>6.003000000000001</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>6.139625000000001</t>
-        </is>
+      <c r="AN26" t="n">
+        <v>6.003000000000001</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>6.139625000000001</v>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
@@ -10686,15 +10586,11 @@
           <t>5.916500000000001</t>
         </is>
       </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>6.005400000000001</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>6.146375000000001</t>
-        </is>
+      <c r="AN27" t="n">
+        <v>6.005400000000001</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>6.146375000000001</v>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
@@ -11073,15 +10969,11 @@
           <t>5.9155</t>
         </is>
       </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>6.0072</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>6.15125</t>
-        </is>
+      <c r="AN28" t="n">
+        <v>6.0072</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>6.15125</v>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
@@ -11460,15 +11352,11 @@
           <t>5.9125</t>
         </is>
       </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>6.0116</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>6.15675</t>
-        </is>
+      <c r="AN29" t="n">
+        <v>6.0116</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>6.15675</v>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
@@ -11847,15 +11735,11 @@
           <t>5.9205</t>
         </is>
       </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>6.021800000000001</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>6.165625</t>
-        </is>
+      <c r="AN30" t="n">
+        <v>6.021800000000001</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>6.165625</v>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
@@ -12234,15 +12118,11 @@
           <t>5.9215</t>
         </is>
       </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>6.0312</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>6.1715</t>
-        </is>
+      <c r="AN31" t="n">
+        <v>6.0312</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>6.1715</v>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
@@ -12621,15 +12501,11 @@
           <t>51.05499999999999</t>
         </is>
       </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>50.074</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>49.723125</t>
-        </is>
+      <c r="AN32" t="n">
+        <v>50.074</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>49.723125</v>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
@@ -13008,15 +12884,11 @@
           <t>50.795</t>
         </is>
       </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>49.95399999999999</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>49.668125</t>
-        </is>
+      <c r="AN33" t="n">
+        <v>49.95399999999999</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>49.668125</v>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
@@ -13395,15 +13267,11 @@
           <t>50.605</t>
         </is>
       </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>49.848</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>49.63062499999999</t>
-        </is>
+      <c r="AN34" t="n">
+        <v>49.848</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>49.63062499999999</v>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
@@ -13782,15 +13650,11 @@
           <t>50.365</t>
         </is>
       </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>49.748</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>49.589375</t>
-        </is>
+      <c r="AN35" t="n">
+        <v>49.748</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>49.589375</v>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
@@ -14169,15 +14033,11 @@
           <t>50.2</t>
         </is>
       </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>49.678</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>49.566875</t>
-        </is>
+      <c r="AN36" t="n">
+        <v>49.678</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>49.566875</v>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
@@ -14556,15 +14416,11 @@
           <t>50.02</t>
         </is>
       </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>49.58900000000001</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>49.52625</t>
-        </is>
+      <c r="AN37" t="n">
+        <v>49.58900000000001</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>49.52625</v>
       </c>
       <c r="AP37" t="inlineStr">
         <is>
@@ -14943,15 +14799,11 @@
           <t>49.8575</t>
         </is>
       </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>49.508</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>49.490625</t>
-        </is>
+      <c r="AN38" t="n">
+        <v>49.508</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>49.490625</v>
       </c>
       <c r="AP38" t="inlineStr">
         <is>
@@ -15330,15 +15182,11 @@
           <t>49.535</t>
         </is>
       </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>49.364</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>49.415</t>
-        </is>
+      <c r="AN39" t="n">
+        <v>49.364</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>49.415</v>
       </c>
       <c r="AP39" t="inlineStr">
         <is>
@@ -15717,15 +15565,11 @@
           <t>49.47</t>
         </is>
       </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>49.34799999999999</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>49.39375</t>
-        </is>
+      <c r="AN40" t="n">
+        <v>49.34799999999999</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>49.39375</v>
       </c>
       <c r="AP40" t="inlineStr">
         <is>
@@ -16104,15 +15948,11 @@
           <t>49.46749999999999</t>
         </is>
       </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>49.328</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>49.39749999999999</t>
-        </is>
+      <c r="AN41" t="n">
+        <v>49.328</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>49.39749999999999</v>
       </c>
       <c r="AP41" t="inlineStr">
         <is>
@@ -16491,15 +16331,11 @@
           <t>17.9425</t>
         </is>
       </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>16.817</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>16.45625</t>
-        </is>
+      <c r="AN42" t="n">
+        <v>16.817</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>16.45625</v>
       </c>
       <c r="AP42" t="inlineStr">
         <is>
@@ -16878,15 +16714,11 @@
           <t>17.95</t>
         </is>
       </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>16.764</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>16.42875</t>
-        </is>
+      <c r="AN43" t="n">
+        <v>16.764</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>16.42875</v>
       </c>
       <c r="AP43" t="inlineStr">
         <is>
@@ -17265,15 +17097,11 @@
           <t>17.9475</t>
         </is>
       </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>16.715</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>16.404375</t>
-        </is>
+      <c r="AN44" t="n">
+        <v>16.715</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>16.404375</v>
       </c>
       <c r="AP44" t="inlineStr">
         <is>
@@ -17652,15 +17480,11 @@
           <t>17.9425</t>
         </is>
       </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>16.669</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>16.381875</t>
-        </is>
+      <c r="AN45" t="n">
+        <v>16.669</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>16.381875</v>
       </c>
       <c r="AP45" t="inlineStr">
         <is>
@@ -18039,15 +17863,11 @@
           <t>17.92</t>
         </is>
       </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>16.624</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>16.359375</t>
-        </is>
+      <c r="AN46" t="n">
+        <v>16.624</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>16.359375</v>
       </c>
       <c r="AP46" t="inlineStr">
         <is>
@@ -18426,15 +18246,11 @@
           <t>17.895</t>
         </is>
       </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>16.574</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>16.335</t>
-        </is>
+      <c r="AN47" t="n">
+        <v>16.574</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>16.335</v>
       </c>
       <c r="AP47" t="inlineStr">
         <is>
@@ -18813,15 +18629,11 @@
           <t>17.875</t>
         </is>
       </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>16.53</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>16.31125</t>
-        </is>
+      <c r="AN48" t="n">
+        <v>16.53</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>16.31125</v>
       </c>
       <c r="AP48" t="inlineStr">
         <is>
@@ -19200,15 +19012,11 @@
           <t>17.8475</t>
         </is>
       </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>16.485</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>16.288125</t>
-        </is>
+      <c r="AN49" t="n">
+        <v>16.485</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>16.288125</v>
       </c>
       <c r="AP49" t="inlineStr">
         <is>
@@ -19587,15 +19395,11 @@
           <t>17.8125</t>
         </is>
       </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>16.439</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>16.265625</t>
-        </is>
+      <c r="AN50" t="n">
+        <v>16.439</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>16.265625</v>
       </c>
       <c r="AP50" t="inlineStr">
         <is>
@@ -19974,15 +19778,11 @@
           <t>17.775</t>
         </is>
       </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>16.396</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>16.241875</t>
-        </is>
+      <c r="AN51" t="n">
+        <v>16.396</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>16.241875</v>
       </c>
       <c r="AP51" t="inlineStr">
         <is>
@@ -20361,15 +20161,11 @@
           <t>37.4</t>
         </is>
       </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>37.668</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>37.886875</t>
-        </is>
+      <c r="AN52" t="n">
+        <v>37.668</v>
+      </c>
+      <c r="AO52" t="n">
+        <v>37.886875</v>
       </c>
       <c r="AP52" t="inlineStr">
         <is>
@@ -20748,15 +20544,11 @@
           <t>37.3475</t>
         </is>
       </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>37.676</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>37.91125</t>
-        </is>
+      <c r="AN53" t="n">
+        <v>37.676</v>
+      </c>
+      <c r="AO53" t="n">
+        <v>37.91125</v>
       </c>
       <c r="AP53" t="inlineStr">
         <is>
@@ -21135,15 +20927,11 @@
           <t>37.315</t>
         </is>
       </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>37.676</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>37.936875</t>
-        </is>
+      <c r="AN54" t="n">
+        <v>37.676</v>
+      </c>
+      <c r="AO54" t="n">
+        <v>37.936875</v>
       </c>
       <c r="AP54" t="inlineStr">
         <is>
@@ -21522,15 +21310,11 @@
           <t>37.2625</t>
         </is>
       </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>37.652</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>37.95375</t>
-        </is>
+      <c r="AN55" t="n">
+        <v>37.652</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>37.95375</v>
       </c>
       <c r="AP55" t="inlineStr">
         <is>
@@ -21909,15 +21693,11 @@
           <t>37.2475</t>
         </is>
       </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>37.652</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>37.98</t>
-        </is>
+      <c r="AN56" t="n">
+        <v>37.652</v>
+      </c>
+      <c r="AO56" t="n">
+        <v>37.98</v>
       </c>
       <c r="AP56" t="inlineStr">
         <is>
@@ -22296,15 +22076,11 @@
           <t>37.24249999999999</t>
         </is>
       </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>37.648</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>38.00125000000001</t>
-        </is>
+      <c r="AN57" t="n">
+        <v>37.648</v>
+      </c>
+      <c r="AO57" t="n">
+        <v>38.00125000000001</v>
       </c>
       <c r="AP57" t="inlineStr">
         <is>
@@ -22683,15 +22459,11 @@
           <t>37.2525</t>
         </is>
       </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>37.655</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>38.02625</t>
-        </is>
+      <c r="AN58" t="n">
+        <v>37.655</v>
+      </c>
+      <c r="AO58" t="n">
+        <v>38.02625</v>
       </c>
       <c r="AP58" t="inlineStr">
         <is>
@@ -23070,15 +22842,11 @@
           <t>37.2825</t>
         </is>
       </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>37.67</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>38.05562500000001</t>
-        </is>
+      <c r="AN59" t="n">
+        <v>37.67</v>
+      </c>
+      <c r="AO59" t="n">
+        <v>38.05562500000001</v>
       </c>
       <c r="AP59" t="inlineStr">
         <is>
@@ -23457,15 +23225,11 @@
           <t>37.3125</t>
         </is>
       </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>37.688</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>38.08125</t>
-        </is>
+      <c r="AN60" t="n">
+        <v>37.688</v>
+      </c>
+      <c r="AO60" t="n">
+        <v>38.08125</v>
       </c>
       <c r="AP60" t="inlineStr">
         <is>
@@ -23844,15 +23608,11 @@
           <t>37.3625</t>
         </is>
       </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>37.705</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>38.094375</t>
-        </is>
+      <c r="AN61" t="n">
+        <v>37.705</v>
+      </c>
+      <c r="AO61" t="n">
+        <v>38.094375</v>
       </c>
       <c r="AP61" t="inlineStr">
         <is>
@@ -24231,15 +23991,11 @@
           <t>26.2325</t>
         </is>
       </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>26.555</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>26.954375</t>
-        </is>
+      <c r="AN62" t="n">
+        <v>26.555</v>
+      </c>
+      <c r="AO62" t="n">
+        <v>26.954375</v>
       </c>
       <c r="AP62" t="inlineStr">
         <is>
@@ -24618,15 +24374,11 @@
           <t>26.2325</t>
         </is>
       </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>26.589</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>26.989375</t>
-        </is>
+      <c r="AN63" t="n">
+        <v>26.589</v>
+      </c>
+      <c r="AO63" t="n">
+        <v>26.989375</v>
       </c>
       <c r="AP63" t="inlineStr">
         <is>
@@ -25005,15 +24757,11 @@
           <t>26.2625</t>
         </is>
       </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>26.61</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>27.03125</t>
-        </is>
+      <c r="AN64" t="n">
+        <v>26.61</v>
+      </c>
+      <c r="AO64" t="n">
+        <v>27.03125</v>
       </c>
       <c r="AP64" t="inlineStr">
         <is>
@@ -25392,15 +25140,11 @@
           <t>26.305</t>
         </is>
       </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>26.64</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>27.083125</t>
-        </is>
+      <c r="AN65" t="n">
+        <v>26.64</v>
+      </c>
+      <c r="AO65" t="n">
+        <v>27.083125</v>
       </c>
       <c r="AP65" t="inlineStr">
         <is>
@@ -25779,15 +25523,11 @@
           <t>26.335</t>
         </is>
       </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>26.665</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>27.115625</t>
-        </is>
+      <c r="AN66" t="n">
+        <v>26.665</v>
+      </c>
+      <c r="AO66" t="n">
+        <v>27.115625</v>
       </c>
       <c r="AP66" t="inlineStr">
         <is>
@@ -26166,15 +25906,11 @@
           <t>26.3975</t>
         </is>
       </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>26.7</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>27.154375</t>
-        </is>
+      <c r="AN67" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="AO67" t="n">
+        <v>27.154375</v>
       </c>
       <c r="AP67" t="inlineStr">
         <is>
@@ -26553,15 +26289,11 @@
           <t>26.3675</t>
         </is>
       </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>26.728</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>27.200625</t>
-        </is>
+      <c r="AN68" t="n">
+        <v>26.728</v>
+      </c>
+      <c r="AO68" t="n">
+        <v>27.200625</v>
       </c>
       <c r="AP68" t="inlineStr">
         <is>
@@ -26940,15 +26672,11 @@
           <t>26.38</t>
         </is>
       </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>26.76</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>27.24812500000001</t>
-        </is>
+      <c r="AN69" t="n">
+        <v>26.76</v>
+      </c>
+      <c r="AO69" t="n">
+        <v>27.24812500000001</v>
       </c>
       <c r="AP69" t="inlineStr">
         <is>
@@ -27327,15 +27055,11 @@
           <t>26.44</t>
         </is>
       </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>26.788</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>27.291875</t>
-        </is>
+      <c r="AN70" t="n">
+        <v>26.788</v>
+      </c>
+      <c r="AO70" t="n">
+        <v>27.291875</v>
       </c>
       <c r="AP70" t="inlineStr">
         <is>
@@ -27714,15 +27438,11 @@
           <t>26.38</t>
         </is>
       </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>26.795</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>27.31125</t>
-        </is>
+      <c r="AN71" t="n">
+        <v>26.795</v>
+      </c>
+      <c r="AO71" t="n">
+        <v>27.31125</v>
       </c>
       <c r="AP71" t="inlineStr">
         <is>
@@ -28101,15 +27821,11 @@
           <t>8.8545</t>
         </is>
       </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>9.0838</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>9.221250000000001</t>
-        </is>
+      <c r="AN72" t="n">
+        <v>9.0838</v>
+      </c>
+      <c r="AO72" t="n">
+        <v>9.22125</v>
       </c>
       <c r="AP72" t="inlineStr">
         <is>
@@ -28488,15 +28204,11 @@
           <t>8.9</t>
         </is>
       </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>9.1062</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>9.2315</t>
-        </is>
+      <c r="AN73" t="n">
+        <v>9.106199999999999</v>
+      </c>
+      <c r="AO73" t="n">
+        <v>9.2315</v>
       </c>
       <c r="AP73" t="inlineStr">
         <is>
@@ -28875,15 +28587,11 @@
           <t>8.92</t>
         </is>
       </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>9.122</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>9.237375</t>
-        </is>
+      <c r="AN74" t="n">
+        <v>9.122</v>
+      </c>
+      <c r="AO74" t="n">
+        <v>9.237375</v>
       </c>
       <c r="AP74" t="inlineStr">
         <is>
@@ -29262,15 +28970,11 @@
           <t>8.956999999999999</t>
         </is>
       </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>9.1446</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>9.247125</t>
-        </is>
+      <c r="AN75" t="n">
+        <v>9.144600000000001</v>
+      </c>
+      <c r="AO75" t="n">
+        <v>9.247125</v>
       </c>
       <c r="AP75" t="inlineStr">
         <is>
@@ -29649,15 +29353,11 @@
           <t>8.983</t>
         </is>
       </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>9.1558</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>9.253125</t>
-        </is>
+      <c r="AN76" t="n">
+        <v>9.155799999999999</v>
+      </c>
+      <c r="AO76" t="n">
+        <v>9.253125000000001</v>
       </c>
       <c r="AP76" t="inlineStr">
         <is>
@@ -30036,15 +29736,11 @@
           <t>9.011</t>
         </is>
       </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>9.169400000000001</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>9.25975</t>
-        </is>
+      <c r="AN77" t="n">
+        <v>9.1694</v>
+      </c>
+      <c r="AO77" t="n">
+        <v>9.25975</v>
       </c>
       <c r="AP77" t="inlineStr">
         <is>
@@ -30423,15 +30119,11 @@
           <t>9.0355</t>
         </is>
       </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>9.1806</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>9.263625000000001</t>
-        </is>
+      <c r="AN78" t="n">
+        <v>9.1806</v>
+      </c>
+      <c r="AO78" t="n">
+        <v>9.263624999999999</v>
       </c>
       <c r="AP78" t="inlineStr">
         <is>
@@ -30810,15 +30502,11 @@
           <t>9.063500000000001</t>
         </is>
       </c>
-      <c r="AN79" t="inlineStr">
-        <is>
-          <t>9.1974</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>9.268875</t>
-        </is>
+      <c r="AN79" t="n">
+        <v>9.1974</v>
+      </c>
+      <c r="AO79" t="n">
+        <v>9.268875</v>
       </c>
       <c r="AP79" t="inlineStr">
         <is>
@@ -31197,15 +30885,11 @@
           <t>9.094999999999999</t>
         </is>
       </c>
-      <c r="AN80" t="inlineStr">
-        <is>
-          <t>9.2172</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>9.273375</t>
-        </is>
+      <c r="AN80" t="n">
+        <v>9.2172</v>
+      </c>
+      <c r="AO80" t="n">
+        <v>9.273375</v>
       </c>
       <c r="AP80" t="inlineStr">
         <is>
@@ -31584,15 +31268,11 @@
           <t>9.116499999999998</t>
         </is>
       </c>
-      <c r="AN81" t="inlineStr">
-        <is>
-          <t>9.2402</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>9.274875</t>
-        </is>
+      <c r="AN81" t="n">
+        <v>9.2402</v>
+      </c>
+      <c r="AO81" t="n">
+        <v>9.274875</v>
       </c>
       <c r="AP81" t="inlineStr">
         <is>
@@ -31971,15 +31651,11 @@
           <t>52.61499999999999</t>
         </is>
       </c>
-      <c r="AN82" t="inlineStr">
-        <is>
-          <t>53.03400000000001</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>53.08374999999999</t>
-        </is>
+      <c r="AN82" t="n">
+        <v>53.03400000000001</v>
+      </c>
+      <c r="AO82" t="n">
+        <v>53.08374999999999</v>
       </c>
       <c r="AP82" t="inlineStr">
         <is>
@@ -32358,15 +32034,11 @@
           <t>52.55</t>
         </is>
       </c>
-      <c r="AN83" t="inlineStr">
-        <is>
-          <t>53.00599999999999</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>53.11375</t>
-        </is>
+      <c r="AN83" t="n">
+        <v>53.00599999999999</v>
+      </c>
+      <c r="AO83" t="n">
+        <v>53.11375</v>
       </c>
       <c r="AP83" t="inlineStr">
         <is>
@@ -32745,15 +32417,11 @@
           <t>52.45</t>
         </is>
       </c>
-      <c r="AN84" t="inlineStr">
-        <is>
-          <t>52.98399999999999</t>
-        </is>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>53.16625000000001</t>
-        </is>
+      <c r="AN84" t="n">
+        <v>52.98399999999999</v>
+      </c>
+      <c r="AO84" t="n">
+        <v>53.16625000000001</v>
       </c>
       <c r="AP84" t="inlineStr">
         <is>
@@ -33132,15 +32800,11 @@
           <t>52.37</t>
         </is>
       </c>
-      <c r="AN85" t="inlineStr">
-        <is>
-          <t>52.986</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>53.20625</t>
-        </is>
+      <c r="AN85" t="n">
+        <v>52.986</v>
+      </c>
+      <c r="AO85" t="n">
+        <v>53.20625</v>
       </c>
       <c r="AP85" t="inlineStr">
         <is>
@@ -33519,15 +33183,11 @@
           <t>52.275</t>
         </is>
       </c>
-      <c r="AN86" t="inlineStr">
-        <is>
-          <t>52.98</t>
-        </is>
-      </c>
-      <c r="AO86" t="inlineStr">
-        <is>
-          <t>53.21124999999999</t>
-        </is>
+      <c r="AN86" t="n">
+        <v>52.98</v>
+      </c>
+      <c r="AO86" t="n">
+        <v>53.21124999999999</v>
       </c>
       <c r="AP86" t="inlineStr">
         <is>
@@ -33906,15 +33566,11 @@
           <t>52.175</t>
         </is>
       </c>
-      <c r="AN87" t="inlineStr">
-        <is>
-          <t>52.96799999999999</t>
-        </is>
-      </c>
-      <c r="AO87" t="inlineStr">
-        <is>
-          <t>53.2</t>
-        </is>
+      <c r="AN87" t="n">
+        <v>52.96799999999999</v>
+      </c>
+      <c r="AO87" t="n">
+        <v>53.2</v>
       </c>
       <c r="AP87" t="inlineStr">
         <is>
@@ -34293,15 +33949,11 @@
           <t>52.105</t>
         </is>
       </c>
-      <c r="AN88" t="inlineStr">
-        <is>
-          <t>52.98399999999999</t>
-        </is>
-      </c>
-      <c r="AO88" t="inlineStr">
-        <is>
-          <t>53.19125</t>
-        </is>
+      <c r="AN88" t="n">
+        <v>52.98399999999999</v>
+      </c>
+      <c r="AO88" t="n">
+        <v>53.19125</v>
       </c>
       <c r="AP88" t="inlineStr">
         <is>
@@ -34680,15 +34332,11 @@
           <t>52.05</t>
         </is>
       </c>
-      <c r="AN89" t="inlineStr">
-        <is>
-          <t>53.0</t>
-        </is>
-      </c>
-      <c r="AO89" t="inlineStr">
-        <is>
-          <t>53.19499999999999</t>
-        </is>
+      <c r="AN89" t="n">
+        <v>53</v>
+      </c>
+      <c r="AO89" t="n">
+        <v>53.19499999999999</v>
       </c>
       <c r="AP89" t="inlineStr">
         <is>
@@ -35067,15 +34715,11 @@
           <t>52.125</t>
         </is>
       </c>
-      <c r="AN90" t="inlineStr">
-        <is>
-          <t>53.034</t>
-        </is>
-      </c>
-      <c r="AO90" t="inlineStr">
-        <is>
-          <t>53.21124999999999</t>
-        </is>
+      <c r="AN90" t="n">
+        <v>53.034</v>
+      </c>
+      <c r="AO90" t="n">
+        <v>53.21124999999999</v>
       </c>
       <c r="AP90" t="inlineStr">
         <is>
@@ -35454,15 +35098,11 @@
           <t>52.175</t>
         </is>
       </c>
-      <c r="AN91" t="inlineStr">
-        <is>
-          <t>53.066</t>
-        </is>
-      </c>
-      <c r="AO91" t="inlineStr">
-        <is>
-          <t>53.2225</t>
-        </is>
+      <c r="AN91" t="n">
+        <v>53.066</v>
+      </c>
+      <c r="AO91" t="n">
+        <v>53.2225</v>
       </c>
       <c r="AP91" t="inlineStr">
         <is>
@@ -35841,15 +35481,11 @@
           <t>14.0325</t>
         </is>
       </c>
-      <c r="AN92" t="inlineStr">
-        <is>
-          <t>14.333</t>
-        </is>
-      </c>
-      <c r="AO92" t="inlineStr">
-        <is>
-          <t>14.558125</t>
-        </is>
+      <c r="AN92" t="n">
+        <v>14.333</v>
+      </c>
+      <c r="AO92" t="n">
+        <v>14.558125</v>
       </c>
       <c r="AP92" t="inlineStr">
         <is>
@@ -36228,15 +35864,11 @@
           <t>14.04</t>
         </is>
       </c>
-      <c r="AN93" t="inlineStr">
-        <is>
-          <t>14.358</t>
-        </is>
-      </c>
-      <c r="AO93" t="inlineStr">
-        <is>
-          <t>14.580625</t>
-        </is>
+      <c r="AN93" t="n">
+        <v>14.358</v>
+      </c>
+      <c r="AO93" t="n">
+        <v>14.580625</v>
       </c>
       <c r="AP93" t="inlineStr">
         <is>
@@ -36615,15 +36247,11 @@
           <t>14.04</t>
         </is>
       </c>
-      <c r="AN94" t="inlineStr">
-        <is>
-          <t>14.38</t>
-        </is>
-      </c>
-      <c r="AO94" t="inlineStr">
-        <is>
-          <t>14.60375</t>
-        </is>
+      <c r="AN94" t="n">
+        <v>14.38</v>
+      </c>
+      <c r="AO94" t="n">
+        <v>14.60375</v>
       </c>
       <c r="AP94" t="inlineStr">
         <is>
@@ -37002,15 +36630,11 @@
           <t>14.05</t>
         </is>
       </c>
-      <c r="AN95" t="inlineStr">
-        <is>
-          <t>14.401</t>
-        </is>
-      </c>
-      <c r="AO95" t="inlineStr">
-        <is>
-          <t>14.63</t>
-        </is>
+      <c r="AN95" t="n">
+        <v>14.401</v>
+      </c>
+      <c r="AO95" t="n">
+        <v>14.63</v>
       </c>
       <c r="AP95" t="inlineStr">
         <is>
@@ -37389,15 +37013,11 @@
           <t>14.055</t>
         </is>
       </c>
-      <c r="AN96" t="inlineStr">
-        <is>
-          <t>14.418</t>
-        </is>
-      </c>
-      <c r="AO96" t="inlineStr">
-        <is>
-          <t>14.65125</t>
-        </is>
+      <c r="AN96" t="n">
+        <v>14.418</v>
+      </c>
+      <c r="AO96" t="n">
+        <v>14.65125</v>
       </c>
       <c r="AP96" t="inlineStr">
         <is>
@@ -37776,15 +37396,11 @@
           <t>14.0425</t>
         </is>
       </c>
-      <c r="AN97" t="inlineStr">
-        <is>
-          <t>14.428</t>
-        </is>
-      </c>
-      <c r="AO97" t="inlineStr">
-        <is>
-          <t>14.665625</t>
-        </is>
+      <c r="AN97" t="n">
+        <v>14.428</v>
+      </c>
+      <c r="AO97" t="n">
+        <v>14.665625</v>
       </c>
       <c r="AP97" t="inlineStr">
         <is>
@@ -38163,15 +37779,11 @@
           <t>14.03</t>
         </is>
       </c>
-      <c r="AN98" t="inlineStr">
-        <is>
-          <t>14.434</t>
-        </is>
-      </c>
-      <c r="AO98" t="inlineStr">
-        <is>
-          <t>14.67625</t>
-        </is>
+      <c r="AN98" t="n">
+        <v>14.434</v>
+      </c>
+      <c r="AO98" t="n">
+        <v>14.67625</v>
       </c>
       <c r="AP98" t="inlineStr">
         <is>
@@ -38550,15 +38162,11 @@
           <t>14.045</t>
         </is>
       </c>
-      <c r="AN99" t="inlineStr">
-        <is>
-          <t>14.449</t>
-        </is>
-      </c>
-      <c r="AO99" t="inlineStr">
-        <is>
-          <t>14.69625</t>
-        </is>
+      <c r="AN99" t="n">
+        <v>14.449</v>
+      </c>
+      <c r="AO99" t="n">
+        <v>14.69625</v>
       </c>
       <c r="AP99" t="inlineStr">
         <is>
@@ -38937,15 +38545,11 @@
           <t>14.0725</t>
         </is>
       </c>
-      <c r="AN100" t="inlineStr">
-        <is>
-          <t>14.468</t>
-        </is>
-      </c>
-      <c r="AO100" t="inlineStr">
-        <is>
-          <t>14.713125</t>
-        </is>
+      <c r="AN100" t="n">
+        <v>14.468</v>
+      </c>
+      <c r="AO100" t="n">
+        <v>14.713125</v>
       </c>
       <c r="AP100" t="inlineStr">
         <is>
@@ -39324,15 +38928,11 @@
           <t>14.0925</t>
         </is>
       </c>
-      <c r="AN101" t="inlineStr">
-        <is>
-          <t>14.485</t>
-        </is>
-      </c>
-      <c r="AO101" t="inlineStr">
-        <is>
-          <t>14.728125</t>
-        </is>
+      <c r="AN101" t="n">
+        <v>14.485</v>
+      </c>
+      <c r="AO101" t="n">
+        <v>14.728125</v>
       </c>
       <c r="AP101" t="inlineStr">
         <is>
@@ -39711,15 +39311,11 @@
           <t>244.475</t>
         </is>
       </c>
-      <c r="AN102" t="inlineStr">
-        <is>
-          <t>249.04</t>
-        </is>
-      </c>
-      <c r="AO102" t="inlineStr">
-        <is>
-          <t>253.625</t>
-        </is>
+      <c r="AN102" t="n">
+        <v>249.04</v>
+      </c>
+      <c r="AO102" t="n">
+        <v>253.625</v>
       </c>
       <c r="AP102" t="inlineStr">
         <is>
@@ -40098,15 +39694,11 @@
           <t>244.95</t>
         </is>
       </c>
-      <c r="AN103" t="inlineStr">
-        <is>
-          <t>249.39</t>
-        </is>
-      </c>
-      <c r="AO103" t="inlineStr">
-        <is>
-          <t>253.93125</t>
-        </is>
+      <c r="AN103" t="n">
+        <v>249.39</v>
+      </c>
+      <c r="AO103" t="n">
+        <v>253.93125</v>
       </c>
       <c r="AP103" t="inlineStr">
         <is>
@@ -40485,15 +40077,11 @@
           <t>245.425</t>
         </is>
       </c>
-      <c r="AN104" t="inlineStr">
-        <is>
-          <t>249.67</t>
-        </is>
-      </c>
-      <c r="AO104" t="inlineStr">
-        <is>
-          <t>254.21875</t>
-        </is>
+      <c r="AN104" t="n">
+        <v>249.67</v>
+      </c>
+      <c r="AO104" t="n">
+        <v>254.21875</v>
       </c>
       <c r="AP104" t="inlineStr">
         <is>
@@ -40872,15 +40460,11 @@
           <t>245.65</t>
         </is>
       </c>
-      <c r="AN105" t="inlineStr">
-        <is>
-          <t>249.93</t>
-        </is>
-      </c>
-      <c r="AO105" t="inlineStr">
-        <is>
-          <t>254.45625</t>
-        </is>
+      <c r="AN105" t="n">
+        <v>249.93</v>
+      </c>
+      <c r="AO105" t="n">
+        <v>254.45625</v>
       </c>
       <c r="AP105" t="inlineStr">
         <is>
@@ -41259,15 +40843,11 @@
           <t>245.95</t>
         </is>
       </c>
-      <c r="AN106" t="inlineStr">
-        <is>
-          <t>250.21</t>
-        </is>
-      </c>
-      <c r="AO106" t="inlineStr">
-        <is>
-          <t>254.6875</t>
-        </is>
+      <c r="AN106" t="n">
+        <v>250.21</v>
+      </c>
+      <c r="AO106" t="n">
+        <v>254.6875</v>
       </c>
       <c r="AP106" t="inlineStr">
         <is>
@@ -41646,15 +41226,11 @@
           <t>246.15</t>
         </is>
       </c>
-      <c r="AN107" t="inlineStr">
-        <is>
-          <t>250.41</t>
-        </is>
-      </c>
-      <c r="AO107" t="inlineStr">
-        <is>
-          <t>254.8625</t>
-        </is>
+      <c r="AN107" t="n">
+        <v>250.41</v>
+      </c>
+      <c r="AO107" t="n">
+        <v>254.8625</v>
       </c>
       <c r="AP107" t="inlineStr">
         <is>
@@ -42033,15 +41609,11 @@
           <t>246.225</t>
         </is>
       </c>
-      <c r="AN108" t="inlineStr">
-        <is>
-          <t>250.58</t>
-        </is>
-      </c>
-      <c r="AO108" t="inlineStr">
-        <is>
-          <t>254.96875</t>
-        </is>
+      <c r="AN108" t="n">
+        <v>250.58</v>
+      </c>
+      <c r="AO108" t="n">
+        <v>254.96875</v>
       </c>
       <c r="AP108" t="inlineStr">
         <is>
@@ -42420,15 +41992,11 @@
           <t>246.25</t>
         </is>
       </c>
-      <c r="AN109" t="inlineStr">
-        <is>
-          <t>250.8</t>
-        </is>
-      </c>
-      <c r="AO109" t="inlineStr">
-        <is>
-          <t>255.125</t>
-        </is>
+      <c r="AN109" t="n">
+        <v>250.8</v>
+      </c>
+      <c r="AO109" t="n">
+        <v>255.125</v>
       </c>
       <c r="AP109" t="inlineStr">
         <is>
@@ -42807,15 +42375,11 @@
           <t>246.525</t>
         </is>
       </c>
-      <c r="AN110" t="inlineStr">
-        <is>
-          <t>251.09</t>
-        </is>
-      </c>
-      <c r="AO110" t="inlineStr">
-        <is>
-          <t>255.29375</t>
-        </is>
+      <c r="AN110" t="n">
+        <v>251.09</v>
+      </c>
+      <c r="AO110" t="n">
+        <v>255.29375</v>
       </c>
       <c r="AP110" t="inlineStr">
         <is>
@@ -43194,15 +42758,11 @@
           <t>246.825</t>
         </is>
       </c>
-      <c r="AN111" t="inlineStr">
-        <is>
-          <t>251.37</t>
-        </is>
-      </c>
-      <c r="AO111" t="inlineStr">
-        <is>
-          <t>255.475</t>
-        </is>
+      <c r="AN111" t="n">
+        <v>251.37</v>
+      </c>
+      <c r="AO111" t="n">
+        <v>255.475</v>
       </c>
       <c r="AP111" t="inlineStr">
         <is>
@@ -43581,15 +43141,11 @@
           <t>5.060499999999999</t>
         </is>
       </c>
-      <c r="AN112" t="inlineStr">
-        <is>
-          <t>4.9742</t>
-        </is>
-      </c>
-      <c r="AO112" t="inlineStr">
-        <is>
-          <t>4.953625000000001</t>
-        </is>
+      <c r="AN112" t="n">
+        <v>4.9742</v>
+      </c>
+      <c r="AO112" t="n">
+        <v>4.953625000000001</v>
       </c>
       <c r="AP112" t="inlineStr">
         <is>
@@ -43968,15 +43524,11 @@
           <t>5.063</t>
         </is>
       </c>
-      <c r="AN113" t="inlineStr">
-        <is>
-          <t>4.972799999999999</t>
-        </is>
-      </c>
-      <c r="AO113" t="inlineStr">
-        <is>
-          <t>4.95375</t>
-        </is>
+      <c r="AN113" t="n">
+        <v>4.972799999999999</v>
+      </c>
+      <c r="AO113" t="n">
+        <v>4.95375</v>
       </c>
       <c r="AP113" t="inlineStr">
         <is>
@@ -44355,15 +43907,11 @@
           <t>5.065499999999999</t>
         </is>
       </c>
-      <c r="AN114" t="inlineStr">
-        <is>
-          <t>4.9662</t>
-        </is>
-      </c>
-      <c r="AO114" t="inlineStr">
-        <is>
-          <t>4.952875</t>
-        </is>
+      <c r="AN114" t="n">
+        <v>4.9662</v>
+      </c>
+      <c r="AO114" t="n">
+        <v>4.952875</v>
       </c>
       <c r="AP114" t="inlineStr">
         <is>
@@ -44742,15 +44290,11 @@
           <t>5.0695</t>
         </is>
       </c>
-      <c r="AN115" t="inlineStr">
-        <is>
-          <t>4.9588</t>
-        </is>
-      </c>
-      <c r="AO115" t="inlineStr">
-        <is>
-          <t>4.957</t>
-        </is>
+      <c r="AN115" t="n">
+        <v>4.9588</v>
+      </c>
+      <c r="AO115" t="n">
+        <v>4.957</v>
       </c>
       <c r="AP115" t="inlineStr">
         <is>
@@ -45129,15 +44673,11 @@
           <t>5.074</t>
         </is>
       </c>
-      <c r="AN116" t="inlineStr">
-        <is>
-          <t>4.9502</t>
-        </is>
-      </c>
-      <c r="AO116" t="inlineStr">
-        <is>
-          <t>4.960625</t>
-        </is>
+      <c r="AN116" t="n">
+        <v>4.9502</v>
+      </c>
+      <c r="AO116" t="n">
+        <v>4.960625</v>
       </c>
       <c r="AP116" t="inlineStr">
         <is>
@@ -45516,15 +45056,11 @@
           <t>5.0785</t>
         </is>
       </c>
-      <c r="AN117" t="inlineStr">
-        <is>
-          <t>4.9406</t>
-        </is>
-      </c>
-      <c r="AO117" t="inlineStr">
-        <is>
-          <t>4.965125</t>
-        </is>
+      <c r="AN117" t="n">
+        <v>4.9406</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>4.965125</v>
       </c>
       <c r="AP117" t="inlineStr">
         <is>
@@ -45903,15 +45439,11 @@
           <t>5.085</t>
         </is>
       </c>
-      <c r="AN118" t="inlineStr">
-        <is>
-          <t>4.9312</t>
-        </is>
-      </c>
-      <c r="AO118" t="inlineStr">
-        <is>
-          <t>4.97</t>
-        </is>
+      <c r="AN118" t="n">
+        <v>4.9312</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>4.97</v>
       </c>
       <c r="AP118" t="inlineStr">
         <is>
@@ -46290,15 +45822,11 @@
           <t>5.097499999999999</t>
         </is>
       </c>
-      <c r="AN119" t="inlineStr">
-        <is>
-          <t>4.9224</t>
-        </is>
-      </c>
-      <c r="AO119" t="inlineStr">
-        <is>
-          <t>4.975250000000001</t>
-        </is>
+      <c r="AN119" t="n">
+        <v>4.9224</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>4.975250000000001</v>
       </c>
       <c r="AP119" t="inlineStr">
         <is>
@@ -46677,15 +46205,11 @@
           <t>5.1</t>
         </is>
       </c>
-      <c r="AN120" t="inlineStr">
-        <is>
-          <t>4.9174</t>
-        </is>
-      </c>
-      <c r="AO120" t="inlineStr">
-        <is>
-          <t>4.98025</t>
-        </is>
+      <c r="AN120" t="n">
+        <v>4.9174</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>4.98025</v>
       </c>
       <c r="AP120" t="inlineStr">
         <is>
@@ -47064,15 +46588,11 @@
           <t>5.1</t>
         </is>
       </c>
-      <c r="AN121" t="inlineStr">
-        <is>
-          <t>4.9126</t>
-        </is>
-      </c>
-      <c r="AO121" t="inlineStr">
-        <is>
-          <t>4.9815</t>
-        </is>
+      <c r="AN121" t="n">
+        <v>4.9126</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>4.9815</v>
       </c>
       <c r="AP121" t="inlineStr">
         <is>
@@ -47451,15 +46971,11 @@
           <t>21.0175</t>
         </is>
       </c>
-      <c r="AN122" t="inlineStr">
-        <is>
-          <t>20.968</t>
-        </is>
-      </c>
-      <c r="AO122" t="inlineStr">
-        <is>
-          <t>21.115625</t>
-        </is>
+      <c r="AN122" t="n">
+        <v>20.968</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>21.115625</v>
       </c>
       <c r="AP122" t="inlineStr">
         <is>
@@ -47838,15 +47354,11 @@
           <t>21.03</t>
         </is>
       </c>
-      <c r="AN123" t="inlineStr">
-        <is>
-          <t>20.976</t>
-        </is>
-      </c>
-      <c r="AO123" t="inlineStr">
-        <is>
-          <t>21.1275</t>
-        </is>
+      <c r="AN123" t="n">
+        <v>20.976</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>21.1275</v>
       </c>
       <c r="AP123" t="inlineStr">
         <is>
@@ -48225,15 +47737,11 @@
           <t>21.04</t>
         </is>
       </c>
-      <c r="AN124" t="inlineStr">
-        <is>
-          <t>20.982</t>
-        </is>
-      </c>
-      <c r="AO124" t="inlineStr">
-        <is>
-          <t>21.14625</t>
-        </is>
+      <c r="AN124" t="n">
+        <v>20.982</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>21.14625</v>
       </c>
       <c r="AP124" t="inlineStr">
         <is>
@@ -48612,15 +48120,11 @@
           <t>21.0625</t>
         </is>
       </c>
-      <c r="AN125" t="inlineStr">
-        <is>
-          <t>20.99</t>
-        </is>
-      </c>
-      <c r="AO125" t="inlineStr">
-        <is>
-          <t>21.163125</t>
-        </is>
+      <c r="AN125" t="n">
+        <v>20.99</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>21.163125</v>
       </c>
       <c r="AP125" t="inlineStr">
         <is>
@@ -48999,15 +48503,11 @@
           <t>21.0875</t>
         </is>
       </c>
-      <c r="AN126" t="inlineStr">
-        <is>
-          <t>20.998</t>
-        </is>
-      </c>
-      <c r="AO126" t="inlineStr">
-        <is>
-          <t>21.17875</t>
-        </is>
+      <c r="AN126" t="n">
+        <v>20.998</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>21.17875</v>
       </c>
       <c r="AP126" t="inlineStr">
         <is>
@@ -49386,15 +48886,11 @@
           <t>21.0925</t>
         </is>
       </c>
-      <c r="AN127" t="inlineStr">
-        <is>
-          <t>21.003</t>
-        </is>
-      </c>
-      <c r="AO127" t="inlineStr">
-        <is>
-          <t>21.200625</t>
-        </is>
+      <c r="AN127" t="n">
+        <v>21.003</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>21.200625</v>
       </c>
       <c r="AP127" t="inlineStr">
         <is>
@@ -49773,15 +49269,11 @@
           <t>21.1</t>
         </is>
       </c>
-      <c r="AN128" t="inlineStr">
-        <is>
-          <t>21.006</t>
-        </is>
-      </c>
-      <c r="AO128" t="inlineStr">
-        <is>
-          <t>21.21375</t>
-        </is>
+      <c r="AN128" t="n">
+        <v>21.006</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>21.21375</v>
       </c>
       <c r="AP128" t="inlineStr">
         <is>
@@ -50160,15 +49652,11 @@
           <t>21.1</t>
         </is>
       </c>
-      <c r="AN129" t="inlineStr">
-        <is>
-          <t>21.004</t>
-        </is>
-      </c>
-      <c r="AO129" t="inlineStr">
-        <is>
-          <t>21.23375</t>
-        </is>
+      <c r="AN129" t="n">
+        <v>21.004</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>21.23375</v>
       </c>
       <c r="AP129" t="inlineStr">
         <is>
@@ -50547,15 +50035,11 @@
           <t>21.1075</t>
         </is>
       </c>
-      <c r="AN130" t="inlineStr">
-        <is>
-          <t>21.013</t>
-        </is>
-      </c>
-      <c r="AO130" t="inlineStr">
-        <is>
-          <t>21.255625</t>
-        </is>
+      <c r="AN130" t="n">
+        <v>21.013</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>21.255625</v>
       </c>
       <c r="AP130" t="inlineStr">
         <is>
@@ -50934,15 +50418,11 @@
           <t>21.1075</t>
         </is>
       </c>
-      <c r="AN131" t="inlineStr">
-        <is>
-          <t>21.019</t>
-        </is>
-      </c>
-      <c r="AO131" t="inlineStr">
-        <is>
-          <t>21.26125</t>
-        </is>
+      <c r="AN131" t="n">
+        <v>21.019</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>21.26125</v>
       </c>
       <c r="AP131" t="inlineStr">
         <is>
@@ -51321,15 +50801,11 @@
           <t>20.17</t>
         </is>
       </c>
-      <c r="AN132" t="inlineStr">
-        <is>
-          <t>20.047</t>
-        </is>
-      </c>
-      <c r="AO132" t="inlineStr">
-        <is>
-          <t>19.9925</t>
-        </is>
+      <c r="AN132" t="n">
+        <v>20.047</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>19.9925</v>
       </c>
       <c r="AP132" t="inlineStr">
         <is>
@@ -51708,15 +51184,11 @@
           <t>20.1575</t>
         </is>
       </c>
-      <c r="AN133" t="inlineStr">
-        <is>
-          <t>20.035</t>
-        </is>
-      </c>
-      <c r="AO133" t="inlineStr">
-        <is>
-          <t>19.98625</t>
-        </is>
+      <c r="AN133" t="n">
+        <v>20.035</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>19.98625</v>
       </c>
       <c r="AP133" t="inlineStr">
         <is>
@@ -52095,15 +51567,11 @@
           <t>20.1375</t>
         </is>
       </c>
-      <c r="AN134" t="inlineStr">
-        <is>
-          <t>20.025</t>
-        </is>
-      </c>
-      <c r="AO134" t="inlineStr">
-        <is>
-          <t>19.97875</t>
-        </is>
+      <c r="AN134" t="n">
+        <v>20.025</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>19.97875</v>
       </c>
       <c r="AP134" t="inlineStr">
         <is>
@@ -52482,15 +51950,11 @@
           <t>20.1025</t>
         </is>
       </c>
-      <c r="AN135" t="inlineStr">
-        <is>
-          <t>20.015</t>
-        </is>
-      </c>
-      <c r="AO135" t="inlineStr">
-        <is>
-          <t>19.969375</t>
-        </is>
+      <c r="AN135" t="n">
+        <v>20.015</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>19.969375</v>
       </c>
       <c r="AP135" t="inlineStr">
         <is>
@@ -52869,15 +52333,11 @@
           <t>20.07</t>
         </is>
       </c>
-      <c r="AN136" t="inlineStr">
-        <is>
-          <t>20.005</t>
-        </is>
-      </c>
-      <c r="AO136" t="inlineStr">
-        <is>
-          <t>19.96125</t>
-        </is>
+      <c r="AN136" t="n">
+        <v>20.005</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>19.96125</v>
       </c>
       <c r="AP136" t="inlineStr">
         <is>
@@ -53256,15 +52716,11 @@
           <t>20.035</t>
         </is>
       </c>
-      <c r="AN137" t="inlineStr">
-        <is>
-          <t>20.001</t>
-        </is>
-      </c>
-      <c r="AO137" t="inlineStr">
-        <is>
-          <t>19.954375</t>
-        </is>
+      <c r="AN137" t="n">
+        <v>20.001</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>19.954375</v>
       </c>
       <c r="AP137" t="inlineStr">
         <is>
@@ -53643,15 +53099,11 @@
           <t>20.01</t>
         </is>
       </c>
-      <c r="AN138" t="inlineStr">
-        <is>
-          <t>19.999</t>
-        </is>
-      </c>
-      <c r="AO138" t="inlineStr">
-        <is>
-          <t>19.9475</t>
-        </is>
+      <c r="AN138" t="n">
+        <v>19.999</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>19.9475</v>
       </c>
       <c r="AP138" t="inlineStr">
         <is>
@@ -54030,15 +53482,11 @@
           <t>19.9775</t>
         </is>
       </c>
-      <c r="AN139" t="inlineStr">
-        <is>
-          <t>19.996</t>
-        </is>
-      </c>
-      <c r="AO139" t="inlineStr">
-        <is>
-          <t>19.939375</t>
-        </is>
+      <c r="AN139" t="n">
+        <v>19.996</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>19.939375</v>
       </c>
       <c r="AP139" t="inlineStr">
         <is>
@@ -54417,15 +53865,11 @@
           <t>19.9475</t>
         </is>
       </c>
-      <c r="AN140" t="inlineStr">
-        <is>
-          <t>19.998</t>
-        </is>
-      </c>
-      <c r="AO140" t="inlineStr">
-        <is>
-          <t>19.933125</t>
-        </is>
+      <c r="AN140" t="n">
+        <v>19.998</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>19.933125</v>
       </c>
       <c r="AP140" t="inlineStr">
         <is>
@@ -54804,15 +54248,11 @@
           <t>19.92</t>
         </is>
       </c>
-      <c r="AN141" t="inlineStr">
-        <is>
-          <t>19.998</t>
-        </is>
-      </c>
-      <c r="AO141" t="inlineStr">
-        <is>
-          <t>19.925</t>
-        </is>
+      <c r="AN141" t="n">
+        <v>19.998</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>19.925</v>
       </c>
       <c r="AP141" t="inlineStr">
         <is>
@@ -55191,15 +54631,11 @@
           <t>13.8925</t>
         </is>
       </c>
-      <c r="AN142" t="inlineStr">
-        <is>
-          <t>14.576</t>
-        </is>
-      </c>
-      <c r="AO142" t="inlineStr">
-        <is>
-          <t>14.915</t>
-        </is>
+      <c r="AN142" t="n">
+        <v>14.576</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>14.915</v>
       </c>
       <c r="AP142" t="inlineStr">
         <is>
@@ -55578,15 +55014,11 @@
           <t>13.96</t>
         </is>
       </c>
-      <c r="AN143" t="inlineStr">
-        <is>
-          <t>14.602</t>
-        </is>
-      </c>
-      <c r="AO143" t="inlineStr">
-        <is>
-          <t>14.944375</t>
-        </is>
+      <c r="AN143" t="n">
+        <v>14.602</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>14.944375</v>
       </c>
       <c r="AP143" t="inlineStr">
         <is>
@@ -55965,15 +55397,11 @@
           <t>14.03</t>
         </is>
       </c>
-      <c r="AN144" t="inlineStr">
-        <is>
-          <t>14.629</t>
-        </is>
-      </c>
-      <c r="AO144" t="inlineStr">
-        <is>
-          <t>14.97375</t>
-        </is>
+      <c r="AN144" t="n">
+        <v>14.629</v>
+      </c>
+      <c r="AO144" t="n">
+        <v>14.97375</v>
       </c>
       <c r="AP144" t="inlineStr">
         <is>
@@ -56352,15 +55780,11 @@
           <t>14.09</t>
         </is>
       </c>
-      <c r="AN145" t="inlineStr">
-        <is>
-          <t>14.652</t>
-        </is>
-      </c>
-      <c r="AO145" t="inlineStr">
-        <is>
-          <t>15.00125</t>
-        </is>
+      <c r="AN145" t="n">
+        <v>14.652</v>
+      </c>
+      <c r="AO145" t="n">
+        <v>15.00125</v>
       </c>
       <c r="AP145" t="inlineStr">
         <is>
@@ -56739,15 +56163,11 @@
           <t>14.15</t>
         </is>
       </c>
-      <c r="AN146" t="inlineStr">
-        <is>
-          <t>14.676</t>
-        </is>
-      </c>
-      <c r="AO146" t="inlineStr">
-        <is>
-          <t>15.028125</t>
-        </is>
+      <c r="AN146" t="n">
+        <v>14.676</v>
+      </c>
+      <c r="AO146" t="n">
+        <v>15.028125</v>
       </c>
       <c r="AP146" t="inlineStr">
         <is>
@@ -57126,15 +56546,11 @@
           <t>14.2125</t>
         </is>
       </c>
-      <c r="AN147" t="inlineStr">
-        <is>
-          <t>14.712</t>
-        </is>
-      </c>
-      <c r="AO147" t="inlineStr">
-        <is>
-          <t>15.05625</t>
-        </is>
+      <c r="AN147" t="n">
+        <v>14.712</v>
+      </c>
+      <c r="AO147" t="n">
+        <v>15.05625</v>
       </c>
       <c r="AP147" t="inlineStr">
         <is>
@@ -57513,15 +56929,11 @@
           <t>14.275</t>
         </is>
       </c>
-      <c r="AN148" t="inlineStr">
-        <is>
-          <t>14.751</t>
-        </is>
-      </c>
-      <c r="AO148" t="inlineStr">
-        <is>
-          <t>15.085</t>
-        </is>
+      <c r="AN148" t="n">
+        <v>14.751</v>
+      </c>
+      <c r="AO148" t="n">
+        <v>15.085</v>
       </c>
       <c r="AP148" t="inlineStr">
         <is>
@@ -57900,15 +57312,11 @@
           <t>14.33</t>
         </is>
       </c>
-      <c r="AN149" t="inlineStr">
-        <is>
-          <t>14.783</t>
-        </is>
-      </c>
-      <c r="AO149" t="inlineStr">
-        <is>
-          <t>15.11125</t>
-        </is>
+      <c r="AN149" t="n">
+        <v>14.783</v>
+      </c>
+      <c r="AO149" t="n">
+        <v>15.11125</v>
       </c>
       <c r="AP149" t="inlineStr">
         <is>
@@ -58287,15 +57695,11 @@
           <t>14.38</t>
         </is>
       </c>
-      <c r="AN150" t="inlineStr">
-        <is>
-          <t>14.816</t>
-        </is>
-      </c>
-      <c r="AO150" t="inlineStr">
-        <is>
-          <t>15.1375</t>
-        </is>
+      <c r="AN150" t="n">
+        <v>14.816</v>
+      </c>
+      <c r="AO150" t="n">
+        <v>15.1375</v>
       </c>
       <c r="AP150" t="inlineStr">
         <is>
@@ -58674,15 +58078,11 @@
           <t>14.4375</t>
         </is>
       </c>
-      <c r="AN151" t="inlineStr">
-        <is>
-          <t>14.848</t>
-        </is>
-      </c>
-      <c r="AO151" t="inlineStr">
-        <is>
-          <t>15.164375</t>
-        </is>
+      <c r="AN151" t="n">
+        <v>14.848</v>
+      </c>
+      <c r="AO151" t="n">
+        <v>15.164375</v>
       </c>
       <c r="AP151" t="inlineStr">
         <is>
@@ -59061,15 +58461,11 @@
           <t>13.0225</t>
         </is>
       </c>
-      <c r="AN152" t="inlineStr">
-        <is>
-          <t>12.726</t>
-        </is>
-      </c>
-      <c r="AO152" t="inlineStr">
-        <is>
-          <t>12.525</t>
-        </is>
+      <c r="AN152" t="n">
+        <v>12.726</v>
+      </c>
+      <c r="AO152" t="n">
+        <v>12.525</v>
       </c>
       <c r="AP152" t="inlineStr">
         <is>
@@ -59448,15 +58844,11 @@
           <t>12.9125</t>
         </is>
       </c>
-      <c r="AN153" t="inlineStr">
-        <is>
-          <t>12.686</t>
-        </is>
-      </c>
-      <c r="AO153" t="inlineStr">
-        <is>
-          <t>12.504375</t>
-        </is>
+      <c r="AN153" t="n">
+        <v>12.686</v>
+      </c>
+      <c r="AO153" t="n">
+        <v>12.504375</v>
       </c>
       <c r="AP153" t="inlineStr">
         <is>
@@ -59835,15 +59227,11 @@
           <t>12.8075</t>
         </is>
       </c>
-      <c r="AN154" t="inlineStr">
-        <is>
-          <t>12.654</t>
-        </is>
-      </c>
-      <c r="AO154" t="inlineStr">
-        <is>
-          <t>12.485</t>
-        </is>
+      <c r="AN154" t="n">
+        <v>12.654</v>
+      </c>
+      <c r="AO154" t="n">
+        <v>12.485</v>
       </c>
       <c r="AP154" t="inlineStr">
         <is>
@@ -60222,15 +59610,11 @@
           <t>12.685</t>
         </is>
       </c>
-      <c r="AN155" t="inlineStr">
-        <is>
-          <t>12.604</t>
-        </is>
-      </c>
-      <c r="AO155" t="inlineStr">
-        <is>
-          <t>12.45875</t>
-        </is>
+      <c r="AN155" t="n">
+        <v>12.604</v>
+      </c>
+      <c r="AO155" t="n">
+        <v>12.45875</v>
       </c>
       <c r="AP155" t="inlineStr">
         <is>
@@ -60609,15 +59993,11 @@
           <t>12.55</t>
         </is>
       </c>
-      <c r="AN156" t="inlineStr">
-        <is>
-          <t>12.546</t>
-        </is>
-      </c>
-      <c r="AO156" t="inlineStr">
-        <is>
-          <t>12.428125</t>
-        </is>
+      <c r="AN156" t="n">
+        <v>12.546</v>
+      </c>
+      <c r="AO156" t="n">
+        <v>12.428125</v>
       </c>
       <c r="AP156" t="inlineStr">
         <is>
@@ -60996,15 +60376,11 @@
           <t>12.4075</t>
         </is>
       </c>
-      <c r="AN157" t="inlineStr">
-        <is>
-          <t>12.488</t>
-        </is>
-      </c>
-      <c r="AO157" t="inlineStr">
-        <is>
-          <t>12.3975</t>
-        </is>
+      <c r="AN157" t="n">
+        <v>12.488</v>
+      </c>
+      <c r="AO157" t="n">
+        <v>12.3975</v>
       </c>
       <c r="AP157" t="inlineStr">
         <is>
@@ -61383,15 +60759,11 @@
           <t>12.3325</t>
         </is>
       </c>
-      <c r="AN158" t="inlineStr">
-        <is>
-          <t>12.458</t>
-        </is>
-      </c>
-      <c r="AO158" t="inlineStr">
-        <is>
-          <t>12.38125</t>
-        </is>
+      <c r="AN158" t="n">
+        <v>12.458</v>
+      </c>
+      <c r="AO158" t="n">
+        <v>12.38125</v>
       </c>
       <c r="AP158" t="inlineStr">
         <is>
@@ -61770,15 +61142,11 @@
           <t>12.2675</t>
         </is>
       </c>
-      <c r="AN159" t="inlineStr">
-        <is>
-          <t>12.433</t>
-        </is>
-      </c>
-      <c r="AO159" t="inlineStr">
-        <is>
-          <t>12.370625</t>
-        </is>
+      <c r="AN159" t="n">
+        <v>12.433</v>
+      </c>
+      <c r="AO159" t="n">
+        <v>12.370625</v>
       </c>
       <c r="AP159" t="inlineStr">
         <is>
@@ -62157,15 +61525,11 @@
           <t>12.2525</t>
         </is>
       </c>
-      <c r="AN160" t="inlineStr">
-        <is>
-          <t>12.424</t>
-        </is>
-      </c>
-      <c r="AO160" t="inlineStr">
-        <is>
-          <t>12.369375</t>
-        </is>
+      <c r="AN160" t="n">
+        <v>12.424</v>
+      </c>
+      <c r="AO160" t="n">
+        <v>12.369375</v>
       </c>
       <c r="AP160" t="inlineStr">
         <is>
@@ -62544,15 +61908,11 @@
           <t>12.24</t>
         </is>
       </c>
-      <c r="AN161" t="inlineStr">
-        <is>
-          <t>12.416</t>
-        </is>
-      </c>
-      <c r="AO161" t="inlineStr">
-        <is>
-          <t>12.365625</t>
-        </is>
+      <c r="AN161" t="n">
+        <v>12.416</v>
+      </c>
+      <c r="AO161" t="n">
+        <v>12.365625</v>
       </c>
       <c r="AP161" t="inlineStr">
         <is>
@@ -62931,15 +62291,11 @@
           <t>22.0425</t>
         </is>
       </c>
-      <c r="AN162" t="inlineStr">
-        <is>
-          <t>21.726</t>
-        </is>
-      </c>
-      <c r="AO162" t="inlineStr">
-        <is>
-          <t>21.606875</t>
-        </is>
+      <c r="AN162" t="n">
+        <v>21.726</v>
+      </c>
+      <c r="AO162" t="n">
+        <v>21.606875</v>
       </c>
       <c r="AP162" t="inlineStr">
         <is>
@@ -63318,15 +62674,11 @@
           <t>22.0825</t>
         </is>
       </c>
-      <c r="AN163" t="inlineStr">
-        <is>
-          <t>21.715</t>
-        </is>
-      </c>
-      <c r="AO163" t="inlineStr">
-        <is>
-          <t>21.6075</t>
-        </is>
+      <c r="AN163" t="n">
+        <v>21.715</v>
+      </c>
+      <c r="AO163" t="n">
+        <v>21.6075</v>
       </c>
       <c r="AP163" t="inlineStr">
         <is>
@@ -63705,15 +63057,11 @@
           <t>22.105</t>
         </is>
       </c>
-      <c r="AN164" t="inlineStr">
-        <is>
-          <t>21.7</t>
-        </is>
-      </c>
-      <c r="AO164" t="inlineStr">
-        <is>
-          <t>21.606875</t>
-        </is>
+      <c r="AN164" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="AO164" t="n">
+        <v>21.606875</v>
       </c>
       <c r="AP164" t="inlineStr">
         <is>
@@ -64092,15 +63440,11 @@
           <t>22.13</t>
         </is>
       </c>
-      <c r="AN165" t="inlineStr">
-        <is>
-          <t>21.683</t>
-        </is>
-      </c>
-      <c r="AO165" t="inlineStr">
-        <is>
-          <t>21.605</t>
-        </is>
+      <c r="AN165" t="n">
+        <v>21.683</v>
+      </c>
+      <c r="AO165" t="n">
+        <v>21.605</v>
       </c>
       <c r="AP165" t="inlineStr">
         <is>
@@ -64479,15 +63823,11 @@
           <t>22.1375</t>
         </is>
       </c>
-      <c r="AN166" t="inlineStr">
-        <is>
-          <t>21.66</t>
-        </is>
-      </c>
-      <c r="AO166" t="inlineStr">
-        <is>
-          <t>21.599375</t>
-        </is>
+      <c r="AN166" t="n">
+        <v>21.66</v>
+      </c>
+      <c r="AO166" t="n">
+        <v>21.599375</v>
       </c>
       <c r="AP166" t="inlineStr">
         <is>
@@ -64866,15 +64206,11 @@
           <t>22.1325</t>
         </is>
       </c>
-      <c r="AN167" t="inlineStr">
-        <is>
-          <t>21.641</t>
-        </is>
-      </c>
-      <c r="AO167" t="inlineStr">
-        <is>
-          <t>21.5875</t>
-        </is>
+      <c r="AN167" t="n">
+        <v>21.641</v>
+      </c>
+      <c r="AO167" t="n">
+        <v>21.5875</v>
       </c>
       <c r="AP167" t="inlineStr">
         <is>
@@ -65253,15 +64589,11 @@
           <t>22.1275</t>
         </is>
       </c>
-      <c r="AN168" t="inlineStr">
-        <is>
-          <t>21.622</t>
-        </is>
-      </c>
-      <c r="AO168" t="inlineStr">
-        <is>
-          <t>21.576875</t>
-        </is>
+      <c r="AN168" t="n">
+        <v>21.622</v>
+      </c>
+      <c r="AO168" t="n">
+        <v>21.576875</v>
       </c>
       <c r="AP168" t="inlineStr">
         <is>
@@ -65640,15 +64972,11 @@
           <t>22.1225</t>
         </is>
       </c>
-      <c r="AN169" t="inlineStr">
-        <is>
-          <t>21.61</t>
-        </is>
-      </c>
-      <c r="AO169" t="inlineStr">
-        <is>
-          <t>21.57375</t>
-        </is>
+      <c r="AN169" t="n">
+        <v>21.61</v>
+      </c>
+      <c r="AO169" t="n">
+        <v>21.57375</v>
       </c>
       <c r="AP169" t="inlineStr">
         <is>
@@ -66027,15 +65355,11 @@
           <t>22.1225</t>
         </is>
       </c>
-      <c r="AN170" t="inlineStr">
-        <is>
-          <t>21.598</t>
-        </is>
-      </c>
-      <c r="AO170" t="inlineStr">
-        <is>
-          <t>21.564375</t>
-        </is>
+      <c r="AN170" t="n">
+        <v>21.598</v>
+      </c>
+      <c r="AO170" t="n">
+        <v>21.564375</v>
       </c>
       <c r="AP170" t="inlineStr">
         <is>
@@ -66414,15 +65738,11 @@
           <t>22.1225</t>
         </is>
       </c>
-      <c r="AN171" t="inlineStr">
-        <is>
-          <t>21.587</t>
-        </is>
-      </c>
-      <c r="AO171" t="inlineStr">
-        <is>
-          <t>21.55</t>
-        </is>
+      <c r="AN171" t="n">
+        <v>21.587</v>
+      </c>
+      <c r="AO171" t="n">
+        <v>21.55</v>
       </c>
       <c r="AP171" t="inlineStr">
         <is>
@@ -66801,15 +66121,11 @@
           <t>25.345</t>
         </is>
       </c>
-      <c r="AN172" t="inlineStr">
-        <is>
-          <t>25.605</t>
-        </is>
-      </c>
-      <c r="AO172" t="inlineStr">
-        <is>
-          <t>25.800625</t>
-        </is>
+      <c r="AN172" t="n">
+        <v>25.605</v>
+      </c>
+      <c r="AO172" t="n">
+        <v>25.800625</v>
       </c>
       <c r="AP172" t="inlineStr">
         <is>
@@ -67188,15 +66504,11 @@
           <t>25.3825</t>
         </is>
       </c>
-      <c r="AN173" t="inlineStr">
-        <is>
-          <t>25.629</t>
-        </is>
-      </c>
-      <c r="AO173" t="inlineStr">
-        <is>
-          <t>25.82375</t>
-        </is>
+      <c r="AN173" t="n">
+        <v>25.629</v>
+      </c>
+      <c r="AO173" t="n">
+        <v>25.82375</v>
       </c>
       <c r="AP173" t="inlineStr">
         <is>
@@ -67575,15 +66887,11 @@
           <t>25.425</t>
         </is>
       </c>
-      <c r="AN174" t="inlineStr">
-        <is>
-          <t>25.655</t>
-        </is>
-      </c>
-      <c r="AO174" t="inlineStr">
-        <is>
-          <t>25.85</t>
-        </is>
+      <c r="AN174" t="n">
+        <v>25.655</v>
+      </c>
+      <c r="AO174" t="n">
+        <v>25.85</v>
       </c>
       <c r="AP174" t="inlineStr">
         <is>
@@ -67962,15 +67270,11 @@
           <t>25.4825</t>
         </is>
       </c>
-      <c r="AN175" t="inlineStr">
-        <is>
-          <t>25.678</t>
-        </is>
-      </c>
-      <c r="AO175" t="inlineStr">
-        <is>
-          <t>25.87375</t>
-        </is>
+      <c r="AN175" t="n">
+        <v>25.678</v>
+      </c>
+      <c r="AO175" t="n">
+        <v>25.87375</v>
       </c>
       <c r="AP175" t="inlineStr">
         <is>
@@ -68349,15 +67653,11 @@
           <t>25.53</t>
         </is>
       </c>
-      <c r="AN176" t="inlineStr">
-        <is>
-          <t>25.699</t>
-        </is>
-      </c>
-      <c r="AO176" t="inlineStr">
-        <is>
-          <t>25.89625</t>
-        </is>
+      <c r="AN176" t="n">
+        <v>25.699</v>
+      </c>
+      <c r="AO176" t="n">
+        <v>25.89625</v>
       </c>
       <c r="AP176" t="inlineStr">
         <is>
@@ -68736,15 +68036,11 @@
           <t>25.58</t>
         </is>
       </c>
-      <c r="AN177" t="inlineStr">
-        <is>
-          <t>25.719</t>
-        </is>
-      </c>
-      <c r="AO177" t="inlineStr">
-        <is>
-          <t>25.91875</t>
-        </is>
+      <c r="AN177" t="n">
+        <v>25.719</v>
+      </c>
+      <c r="AO177" t="n">
+        <v>25.91875</v>
       </c>
       <c r="AP177" t="inlineStr">
         <is>
@@ -69123,15 +68419,11 @@
           <t>25.6175</t>
         </is>
       </c>
-      <c r="AN178" t="inlineStr">
-        <is>
-          <t>25.736</t>
-        </is>
-      </c>
-      <c r="AO178" t="inlineStr">
-        <is>
-          <t>25.93875000000001</t>
-        </is>
+      <c r="AN178" t="n">
+        <v>25.736</v>
+      </c>
+      <c r="AO178" t="n">
+        <v>25.93875000000001</v>
       </c>
       <c r="AP178" t="inlineStr">
         <is>
@@ -69510,15 +68802,11 @@
           <t>25.625</t>
         </is>
       </c>
-      <c r="AN179" t="inlineStr">
-        <is>
-          <t>25.755</t>
-        </is>
-      </c>
-      <c r="AO179" t="inlineStr">
-        <is>
-          <t>25.960625</t>
-        </is>
+      <c r="AN179" t="n">
+        <v>25.755</v>
+      </c>
+      <c r="AO179" t="n">
+        <v>25.960625</v>
       </c>
       <c r="AP179" t="inlineStr">
         <is>
@@ -69897,15 +69185,11 @@
           <t>25.625</t>
         </is>
       </c>
-      <c r="AN180" t="inlineStr">
-        <is>
-          <t>25.778</t>
-        </is>
-      </c>
-      <c r="AO180" t="inlineStr">
-        <is>
-          <t>25.98125</t>
-        </is>
+      <c r="AN180" t="n">
+        <v>25.778</v>
+      </c>
+      <c r="AO180" t="n">
+        <v>25.98125</v>
       </c>
       <c r="AP180" t="inlineStr">
         <is>
@@ -70284,15 +69568,11 @@
           <t>25.6275</t>
         </is>
       </c>
-      <c r="AN181" t="inlineStr">
-        <is>
-          <t>25.789</t>
-        </is>
-      </c>
-      <c r="AO181" t="inlineStr">
-        <is>
-          <t>25.989375</t>
-        </is>
+      <c r="AN181" t="n">
+        <v>25.789</v>
+      </c>
+      <c r="AO181" t="n">
+        <v>25.989375</v>
       </c>
       <c r="AP181" t="inlineStr">
         <is>
@@ -70671,15 +69951,11 @@
           <t>5.816</t>
         </is>
       </c>
-      <c r="AN182" t="inlineStr">
-        <is>
-          <t>5.8766</t>
-        </is>
-      </c>
-      <c r="AO182" t="inlineStr">
-        <is>
-          <t>5.90375</t>
-        </is>
+      <c r="AN182" t="n">
+        <v>5.8766</v>
+      </c>
+      <c r="AO182" t="n">
+        <v>5.90375</v>
       </c>
       <c r="AP182" t="inlineStr">
         <is>
@@ -71058,15 +70334,11 @@
           <t>5.8155</t>
         </is>
       </c>
-      <c r="AN183" t="inlineStr">
-        <is>
-          <t>5.8872</t>
-        </is>
-      </c>
-      <c r="AO183" t="inlineStr">
-        <is>
-          <t>5.9055</t>
-        </is>
+      <c r="AN183" t="n">
+        <v>5.8872</v>
+      </c>
+      <c r="AO183" t="n">
+        <v>5.9055</v>
       </c>
       <c r="AP183" t="inlineStr">
         <is>
@@ -71445,15 +70717,11 @@
           <t>5.81</t>
         </is>
       </c>
-      <c r="AN184" t="inlineStr">
-        <is>
-          <t>5.894</t>
-        </is>
-      </c>
-      <c r="AO184" t="inlineStr">
-        <is>
-          <t>5.907125</t>
-        </is>
+      <c r="AN184" t="n">
+        <v>5.894</v>
+      </c>
+      <c r="AO184" t="n">
+        <v>5.907125</v>
       </c>
       <c r="AP184" t="inlineStr">
         <is>
@@ -71832,15 +71100,11 @@
           <t>5.811500000000001</t>
         </is>
       </c>
-      <c r="AN185" t="inlineStr">
-        <is>
-          <t>5.903</t>
-        </is>
-      </c>
-      <c r="AO185" t="inlineStr">
-        <is>
-          <t>5.911499999999999</t>
-        </is>
+      <c r="AN185" t="n">
+        <v>5.903</v>
+      </c>
+      <c r="AO185" t="n">
+        <v>5.911499999999999</v>
       </c>
       <c r="AP185" t="inlineStr">
         <is>
@@ -72219,15 +71483,11 @@
           <t>5.8085</t>
         </is>
       </c>
-      <c r="AN186" t="inlineStr">
-        <is>
-          <t>5.91</t>
-        </is>
-      </c>
-      <c r="AO186" t="inlineStr">
-        <is>
-          <t>5.91425</t>
-        </is>
+      <c r="AN186" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="AO186" t="n">
+        <v>5.91425</v>
       </c>
       <c r="AP186" t="inlineStr">
         <is>
@@ -72606,15 +71866,11 @@
           <t>5.8055</t>
         </is>
       </c>
-      <c r="AN187" t="inlineStr">
-        <is>
-          <t>5.9182</t>
-        </is>
-      </c>
-      <c r="AO187" t="inlineStr">
-        <is>
-          <t>5.9155</t>
-        </is>
+      <c r="AN187" t="n">
+        <v>5.9182</v>
+      </c>
+      <c r="AO187" t="n">
+        <v>5.9155</v>
       </c>
       <c r="AP187" t="inlineStr">
         <is>
@@ -72993,15 +72249,11 @@
           <t>5.804</t>
         </is>
       </c>
-      <c r="AN188" t="inlineStr">
-        <is>
-          <t>5.923999999999999</t>
-        </is>
-      </c>
-      <c r="AO188" t="inlineStr">
-        <is>
-          <t>5.91575</t>
-        </is>
+      <c r="AN188" t="n">
+        <v>5.923999999999999</v>
+      </c>
+      <c r="AO188" t="n">
+        <v>5.91575</v>
       </c>
       <c r="AP188" t="inlineStr">
         <is>
@@ -73380,15 +72632,11 @@
           <t>5.8085</t>
         </is>
       </c>
-      <c r="AN189" t="inlineStr">
-        <is>
-          <t>5.9288</t>
-        </is>
-      </c>
-      <c r="AO189" t="inlineStr">
-        <is>
-          <t>5.917624999999999</t>
-        </is>
+      <c r="AN189" t="n">
+        <v>5.9288</v>
+      </c>
+      <c r="AO189" t="n">
+        <v>5.917624999999999</v>
       </c>
       <c r="AP189" t="inlineStr">
         <is>
@@ -73767,15 +73015,11 @@
           <t>5.815</t>
         </is>
       </c>
-      <c r="AN190" t="inlineStr">
-        <is>
-          <t>5.933</t>
-        </is>
-      </c>
-      <c r="AO190" t="inlineStr">
-        <is>
-          <t>5.919375</t>
-        </is>
+      <c r="AN190" t="n">
+        <v>5.933</v>
+      </c>
+      <c r="AO190" t="n">
+        <v>5.919375</v>
       </c>
       <c r="AP190" t="inlineStr">
         <is>
@@ -74154,15 +73398,11 @@
           <t>5.8155</t>
         </is>
       </c>
-      <c r="AN191" t="inlineStr">
-        <is>
-          <t>5.936</t>
-        </is>
-      </c>
-      <c r="AO191" t="inlineStr">
-        <is>
-          <t>5.919750000000001</t>
-        </is>
+      <c r="AN191" t="n">
+        <v>5.936</v>
+      </c>
+      <c r="AO191" t="n">
+        <v>5.919750000000001</v>
       </c>
       <c r="AP191" t="inlineStr">
         <is>

--- a/Result/checksun/貿易百貨.xlsx
+++ b/Result/checksun/貿易百貨.xlsx
@@ -5559,7 +5559,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5986,7 +5986,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6413,7 +6413,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6840,7 +6840,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7267,7 +7267,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7694,7 +7694,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8121,7 +8121,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8548,7 +8548,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8973,7 +8973,11 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>8429</t>
@@ -9396,7 +9400,11 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>8429</t>
@@ -9819,7 +9827,11 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr"/>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>8429</t>
@@ -10244,7 +10256,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>價_量;【d1】;【d2】</t>
+          <t>價_量;【d1】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10670,7 +10682,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11096,7 +11108,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11522,7 +11534,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11946,7 +11958,11 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>5907</t>
@@ -12368,7 +12384,11 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>5907</t>
@@ -28991,7 +29011,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -29417,7 +29437,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -29843,7 +29863,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -30269,7 +30289,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -30695,7 +30715,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -31121,7 +31141,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -31545,7 +31565,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr"/>
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>2939</t>
@@ -31967,7 +31991,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr"/>
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>2939</t>
@@ -32389,7 +32417,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr"/>
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>2939</t>
@@ -32811,7 +32843,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr"/>
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>2939</t>
@@ -33233,7 +33269,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr"/>
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>2939</t>
@@ -33655,7 +33695,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr"/>
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B79" t="inlineStr">
         <is>
           <t>2929</t>
@@ -34078,7 +34122,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr"/>
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
           <t>2929</t>
@@ -34501,7 +34549,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr"/>
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
           <t>2929</t>
@@ -34924,7 +34976,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr"/>
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
           <t>2929</t>
@@ -35347,7 +35403,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr"/>
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
           <t>2929</t>
@@ -35770,7 +35830,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr"/>
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
           <t>2929</t>
@@ -36193,7 +36257,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr"/>
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
           <t>2929</t>
@@ -36616,7 +36684,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr"/>
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
           <t>2929</t>
@@ -37039,7 +37111,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr"/>
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
           <t>2929</t>
@@ -43015,7 +43091,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -43446,7 +43522,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -43875,7 +43951,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr"/>
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B103" t="inlineStr">
         <is>
           <t>2913</t>
@@ -44302,7 +44382,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr"/>
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B104" t="inlineStr">
         <is>
           <t>2913</t>
@@ -44729,7 +44813,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr"/>
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B105" t="inlineStr">
         <is>
           <t>2913</t>
@@ -45156,7 +45244,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr"/>
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B106" t="inlineStr">
         <is>
           <t>2913</t>
@@ -47740,7 +47832,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -48166,7 +48258,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -48592,7 +48684,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -49018,7 +49110,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -49444,7 +49536,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -49868,7 +49960,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr"/>
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B117" t="inlineStr">
         <is>
           <t>2912</t>
@@ -50290,7 +50386,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr"/>
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B118" t="inlineStr">
         <is>
           <t>2912</t>
@@ -50712,7 +50812,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr"/>
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B119" t="inlineStr">
         <is>
           <t>2912</t>
@@ -52412,7 +52516,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr"/>
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B123" t="inlineStr">
         <is>
           <t>2911</t>
@@ -59658,7 +59766,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -60085,7 +60193,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -60512,7 +60620,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -60939,7 +61047,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -61366,7 +61474,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -66477,7 +66585,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" t="inlineStr"/>
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B156" t="inlineStr">
         <is>
           <t>2906</t>
@@ -66899,7 +67011,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" t="inlineStr"/>
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B157" t="inlineStr">
         <is>
           <t>2906</t>
@@ -67321,7 +67437,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" t="inlineStr"/>
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B158" t="inlineStr">
         <is>
           <t>2906</t>
@@ -67743,7 +67863,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" t="inlineStr"/>
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B159" t="inlineStr">
         <is>
           <t>2906</t>
@@ -68165,7 +68289,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" t="inlineStr"/>
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B160" t="inlineStr">
         <is>
           <t>2906</t>
@@ -68587,7 +68715,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" t="inlineStr"/>
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B161" t="inlineStr">
         <is>
           <t>2906</t>
@@ -69009,7 +69141,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" t="inlineStr"/>
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B162" t="inlineStr">
         <is>
           <t>2906</t>
@@ -69431,7 +69567,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" t="inlineStr"/>
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B163" t="inlineStr">
         <is>
           <t>2906</t>
@@ -69853,7 +69993,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" t="inlineStr"/>
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B164" t="inlineStr">
         <is>
           <t>2906</t>
@@ -80501,7 +80645,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -80927,7 +81071,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -81353,7 +81497,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -81779,7 +81923,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -82203,7 +82347,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" t="inlineStr"/>
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B193" t="inlineStr">
         <is>
           <t>2901</t>
@@ -82627,7 +82775,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -83051,7 +83199,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" t="inlineStr"/>
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B195" t="inlineStr">
         <is>
           <t>2901</t>
@@ -83473,7 +83625,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" t="inlineStr"/>
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B196" t="inlineStr">
         <is>
           <t>2901</t>
@@ -83895,7 +84051,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" t="inlineStr"/>
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B197" t="inlineStr">
         <is>
           <t>2901</t>
@@ -84317,7 +84477,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" t="inlineStr"/>
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B198" t="inlineStr">
         <is>
           <t>2901</t>
@@ -84739,7 +84903,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" t="inlineStr"/>
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B199" t="inlineStr">
         <is>
           <t>2901</t>
@@ -85163,7 +85331,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>價_量;【d1】;【d2】</t>
+          <t>價_量;【d1】</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -85590,7 +85758,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -86015,7 +86183,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" t="inlineStr"/>
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B202" t="inlineStr">
         <is>
           <t>2601</t>
@@ -86438,7 +86610,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" t="inlineStr"/>
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B203" t="inlineStr">
         <is>
           <t>2601</t>
@@ -86861,7 +87037,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" t="inlineStr"/>
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B204" t="inlineStr">
         <is>
           <t>2601</t>
@@ -87284,7 +87464,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" t="inlineStr"/>
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B205" t="inlineStr">
         <is>
           <t>2601</t>
